--- a/src/nodes/HPC/compressor_blade_parameters.xlsx
+++ b/src/nodes/HPC/compressor_blade_parameters.xlsx
@@ -803,106 +803,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>28.118206703540103</v>
+        <v>28.321637242839358</v>
       </c>
       <c r="E3">
-        <v>27.277725087198327</v>
+        <v>27.259899548519414</v>
       </c>
       <c r="F3">
-        <v>70.739604742402236</v>
+        <v>70.6493051746511</v>
       </c>
       <c r="G3">
-        <v>70.628464807371074</v>
+        <v>70.586764589953845</v>
       </c>
       <c r="H3">
-        <v>37.560841960432178</v>
+        <v>48.292511091984224</v>
       </c>
       <c r="I3">
-        <v>109.32280890054773</v>
+        <v>69.814217961473943</v>
       </c>
       <c r="J3">
-        <v>62.597088467412078</v>
+        <v>80.487169601993415</v>
       </c>
       <c r="K3">
-        <v>53.412476074859008</v>
+        <v>34.980616976303814</v>
       </c>
       <c r="L3">
-        <v>459.47685198649066</v>
+        <v>590.75595255405938</v>
       </c>
       <c r="M3">
-        <v>3485.0998389755068</v>
+        <v>2463.9786960211127</v>
       </c>
       <c r="N3">
-        <v>12.232868807108174</v>
+        <v>12.232868807108176</v>
       </c>
       <c r="O3">
-        <v>31.878981833936816</v>
+        <v>35.29336527669517</v>
       </c>
       <c r="P3">
-        <v>1.6665517917131332</v>
+        <v>1.6666594422619077</v>
       </c>
       <c r="Q3">
-        <v>0.48857577491856247</v>
+        <v>0.50105290867266339</v>
       </c>
       <c r="R3">
-        <v>122.71624921467101</v>
+        <v>164.67148931400143</v>
       </c>
       <c r="S3">
-        <v>58.515565830312774</v>
+        <v>27.082850896314437</v>
       </c>
       <c r="T3">
-        <v>7191.2234535267562</v>
+        <v>9245.8587259629712</v>
       </c>
       <c r="U3">
-        <v>142139.48878733968</v>
+        <v>105910.79076673692</v>
       </c>
       <c r="V3">
-        <v>795.98880992712134</v>
+        <v>1023.4141841920133</v>
       </c>
       <c r="W3">
-        <v>1770.6773829845913</v>
+        <v>1234.5836925488545</v>
       </c>
       <c r="X3">
-        <v>18.394959273279884</v>
+        <v>30.526788115903535</v>
       </c>
       <c r="Y3">
-        <v>32.419523941719355</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="Z3">
-        <v>1570.5034032729534</v>
+        <v>2019.21866135094</v>
       </c>
       <c r="AA3">
-        <v>31038.054331183379</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AB3">
-        <v>30.246838998325174</v>
+        <v>38.825197795362634</v>
       </c>
       <c r="AC3">
-        <v>67.9420284885761</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.1159912849093541</v>
+        <v>1.1180165935167421</v>
       </c>
       <c r="AE3">
-        <v>0.1255502938646294</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.805745227229156</v>
+        <v>29.769093119297569</v>
       </c>
       <c r="AG3">
-        <v>32.270644646107591</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="AH3">
-        <v>1571.0926173190044</v>
+        <v>2019.9763563475462</v>
       </c>
       <c r="AI3">
-        <v>31038.203210478991</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -911,16 +911,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>1588.8983625462336</v>
+        <v>2049.7454494668432</v>
       </c>
       <c r="AM3">
-        <v>31070.4738551251</v>
+        <v>18958.246325081931</v>
       </c>
       <c r="AN3">
-        <v>106.30598317008956</v>
+        <v>137.13906149937242</v>
       </c>
       <c r="AO3">
-        <v>802.62996732164311</v>
+        <v>537.10763923259367</v>
       </c>
       <c r="AP3">
         <v>9.4801451504353054</v>
@@ -940,124 +940,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>28.018713250709638</v>
+        <v>28.229825711877151</v>
       </c>
       <c r="E4">
-        <v>27.102296834965461</v>
+        <v>27.071761041418288</v>
       </c>
       <c r="F4">
-        <v>63.79637077054727</v>
+        <v>63.732492283173976</v>
       </c>
       <c r="G4">
-        <v>63.656039358054585</v>
+        <v>63.638437772222545</v>
       </c>
       <c r="H4">
-        <v>36.927401065004595</v>
+        <v>47.478087083577321</v>
       </c>
       <c r="I4">
-        <v>88.8225275127105</v>
+        <v>59.215018341806989</v>
       </c>
       <c r="J4">
-        <v>67.458484450728932</v>
+        <v>86.73792793371706</v>
       </c>
       <c r="K4">
-        <v>54.756061318240157</v>
+        <v>36.504040878826764</v>
       </c>
       <c r="L4">
-        <v>447.90279610402382</v>
+        <v>575.87502356231641</v>
       </c>
       <c r="M4">
-        <v>2552.3118811767781</v>
+        <v>1701.5412541178519</v>
       </c>
       <c r="N4">
-        <v>12.129280241400279</v>
+        <v>12.129280241400281</v>
       </c>
       <c r="O4">
         <v>28.734961193392547</v>
       </c>
       <c r="P4">
-        <v>1.8267866815750018</v>
+        <v>1.8269044365883842</v>
       </c>
       <c r="Q4">
-        <v>0.61646592200840689</v>
+        <v>0.61646592200840677</v>
       </c>
       <c r="R4">
-        <v>143.13929937715912</v>
+        <v>190.69914932802081</v>
       </c>
       <c r="S4">
-        <v>56.806794491279014</v>
+        <v>30.579178240351204</v>
       </c>
       <c r="T4">
-        <v>6950.7174204389657</v>
+        <v>8936.6366834215278</v>
       </c>
       <c r="U4">
-        <v>93829.508196535928</v>
+        <v>62553.005464357258</v>
       </c>
       <c r="V4">
-        <v>850.46933396312443</v>
+        <v>1093.4605722383028</v>
       </c>
       <c r="W4">
-        <v>1636.1873341296166</v>
+        <v>1090.7915560864108</v>
       </c>
       <c r="X4">
-        <v>19.907038423333169</v>
+        <v>32.23724396542957</v>
       </c>
       <c r="Y4">
-        <v>23.051548665181226</v>
+        <v>8.0756810229526952</v>
       </c>
       <c r="Z4">
-        <v>1517.9788855864927</v>
+        <v>1951.687138611203</v>
       </c>
       <c r="AA4">
-        <v>20488.925337486471</v>
+        <v>13659.283558324305</v>
       </c>
       <c r="AB4">
-        <v>32.246471400090151</v>
+        <v>41.391936771866753</v>
       </c>
       <c r="AC4">
-        <v>62.774037046962746</v>
+        <v>41.849358031308576</v>
       </c>
       <c r="AD4">
-        <v>1.2325487418079597</v>
+        <v>1.2347883954903314</v>
       </c>
       <c r="AE4">
-        <v>0.17573851509306887</v>
+        <v>0.17564464381670725</v>
       </c>
       <c r="AF4">
-        <v>19.213244217584567</v>
+        <v>31.34506311307711</v>
       </c>
       <c r="AG4">
-        <v>22.859006548711257</v>
+        <v>7.9473881770507271</v>
       </c>
       <c r="AH4">
-        <v>1518.6726797922415</v>
+        <v>1952.5793194635558</v>
       </c>
       <c r="AI4">
-        <v>20489.117879602942</v>
+        <v>13659.411851170204</v>
       </c>
       <c r="AJ4">
-        <v>-7.0507433288103095E-15</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>-6.9404441740299753E-15</v>
       </c>
       <c r="AL4">
-        <v>1537.8859240098261</v>
+        <v>1983.9243825766325</v>
       </c>
       <c r="AM4">
-        <v>20511.976886151653</v>
+        <v>13667.359239347255</v>
       </c>
       <c r="AN4">
-        <v>103.62870921633811</v>
+        <v>133.68437731548397</v>
       </c>
       <c r="AO4">
-        <v>587.8082179034426</v>
+        <v>391.66317915221271</v>
       </c>
       <c r="AP4">
         <v>9.39986679101518</v>
@@ -1077,43 +1077,43 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D5">
-        <v>26.976058898859058</v>
+        <v>27.191154191894135</v>
       </c>
       <c r="E5">
-        <v>25.979886567667421</v>
+        <v>25.931469876663538</v>
       </c>
       <c r="F5">
-        <v>56.557931208200259</v>
+        <v>56.498569826328939</v>
       </c>
       <c r="G5">
-        <v>56.416737256794427</v>
+        <v>56.403947728372586</v>
       </c>
       <c r="H5">
-        <v>33.666766708926517</v>
+        <v>43.285842911476941</v>
       </c>
       <c r="I5">
-        <v>69.7722169687325</v>
+        <v>46.514811312488327</v>
       </c>
       <c r="J5">
-        <v>67.486716865014117</v>
+        <v>86.768635969303872</v>
       </c>
       <c r="K5">
-        <v>43.271836046223775</v>
+        <v>28.847890697482509</v>
       </c>
       <c r="L5">
-        <v>389.90856301663251</v>
+        <v>501.31100959281304</v>
       </c>
       <c r="M5">
-        <v>1776.9402929832165</v>
+        <v>1184.6268619888108</v>
       </c>
       <c r="N5">
-        <v>11.581408051081152</v>
+        <v>11.58140805108115</v>
       </c>
       <c r="O5">
         <v>25.467734439046545</v>
@@ -1125,58 +1125,58 @@
         <v>0.62018720238767078</v>
       </c>
       <c r="R5">
-        <v>154.8850352594369</v>
+        <v>204.67610842602153</v>
       </c>
       <c r="S5">
-        <v>41.655430021181168</v>
+        <v>23.273602248626645</v>
       </c>
       <c r="T5">
-        <v>5777.4336340439813</v>
+        <v>7428.1289580565453</v>
       </c>
       <c r="U5">
-        <v>57897.2892944596</v>
+        <v>38598.192862973061</v>
       </c>
       <c r="V5">
-        <v>812.218751320501</v>
+        <v>1044.2812516977867</v>
       </c>
       <c r="W5">
-        <v>1146.0000141920996</v>
+        <v>764.00000946139971</v>
       </c>
       <c r="X5">
-        <v>19.604537651955095</v>
+        <v>30.744040073544944</v>
       </c>
       <c r="Y5">
-        <v>14.818791081495675</v>
+        <v>5.3825096221696533</v>
       </c>
       <c r="Z5">
-        <v>1261.7434631376714</v>
+        <v>1622.2415954627224</v>
       </c>
       <c r="AA5">
-        <v>12642.64579872148</v>
+        <v>8428.4305324809848</v>
       </c>
       <c r="AB5">
-        <v>30.627545278992272</v>
+        <v>39.378272501561611</v>
       </c>
       <c r="AC5">
-        <v>43.964385076910709</v>
+        <v>29.309590051273762</v>
       </c>
       <c r="AD5">
-        <v>1.41160428996194</v>
+        <v>1.4165085019227341</v>
       </c>
       <c r="AE5">
-        <v>0.19947477922290915</v>
+        <v>0.19936829209814289</v>
       </c>
       <c r="AF5">
-        <v>18.849809741603625</v>
+        <v>29.770302994238737</v>
       </c>
       <c r="AG5">
-        <v>14.665728822568124</v>
+        <v>5.2805225902439483</v>
       </c>
       <c r="AH5">
-        <v>1262.4981910480231</v>
+        <v>1623.2153325420291</v>
       </c>
       <c r="AI5">
-        <v>12642.798860980411</v>
+        <v>8428.53251951291</v>
       </c>
       <c r="AJ5">
         <v>5.8605751304312572E-15</v>
@@ -1185,16 +1185,16 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>1281.3480007896264</v>
+        <v>1652.9856355362676</v>
       </c>
       <c r="AM5">
-        <v>12657.464589802978</v>
+        <v>8433.8130421031528</v>
       </c>
       <c r="AN5">
-        <v>90.207792954583979</v>
+        <v>116.37134164603774</v>
       </c>
       <c r="AO5">
-        <v>409.23767750384673</v>
+        <v>272.67973276673973</v>
       </c>
       <c r="AP5">
         <v>8.9752805414598669</v>
@@ -1214,43 +1214,43 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D6">
-        <v>26.176934098656247</v>
+        <v>26.386993270422963</v>
       </c>
       <c r="E6">
-        <v>25.197208770838049</v>
+        <v>25.147980550060186</v>
       </c>
       <c r="F6">
-        <v>51.67246136267908</v>
+        <v>51.618081281948413</v>
       </c>
       <c r="G6">
-        <v>51.542563493307036</v>
+        <v>51.53102983393552</v>
       </c>
       <c r="H6">
-        <v>31.634784972071781</v>
+        <v>40.673294964092285</v>
       </c>
       <c r="I6">
-        <v>58.237071832669386</v>
+        <v>38.824714555112919</v>
       </c>
       <c r="J6">
-        <v>62.442851639252481</v>
+        <v>80.283666393324609</v>
       </c>
       <c r="K6">
-        <v>33.2282012062035</v>
+        <v>22.152134137468991</v>
       </c>
       <c r="L6">
-        <v>355.14686792490596</v>
+        <v>456.61740161773605</v>
       </c>
       <c r="M6">
-        <v>1355.0282421108079</v>
+        <v>903.35216140720513</v>
       </c>
       <c r="N6">
-        <v>11.226466948912126</v>
+        <v>11.226466948912124</v>
       </c>
       <c r="O6">
         <v>23.267451461230138</v>
@@ -1259,79 +1259,79 @@
         <v>1.9738667955030851</v>
       </c>
       <c r="Q6">
-        <v>0.57056785584407421</v>
+        <v>0.570567855844074</v>
       </c>
       <c r="R6">
-        <v>140.91615045249043</v>
+        <v>186.06776357160138</v>
       </c>
       <c r="S6">
-        <v>29.309074342817961</v>
+        <v>16.406627933932498</v>
       </c>
       <c r="T6">
-        <v>5101.0774776157059</v>
+        <v>6558.5281855059075</v>
       </c>
       <c r="U6">
-        <v>40335.945966013336</v>
+        <v>26890.630644008892</v>
       </c>
       <c r="V6">
-        <v>728.46814498257083</v>
+        <v>936.60190069187684</v>
       </c>
       <c r="W6">
-        <v>803.9787294267021</v>
+        <v>535.98581961780121</v>
       </c>
       <c r="X6">
-        <v>17.662278985244562</v>
+        <v>27.598500256571025</v>
       </c>
       <c r="Y6">
-        <v>10.350130827038949</v>
+        <v>3.7673322567464971</v>
       </c>
       <c r="Z6">
-        <v>1114.0329028470894</v>
+        <v>1432.3280179462595</v>
       </c>
       <c r="AA6">
-        <v>8807.8921141041137</v>
+        <v>5871.9280760694064</v>
       </c>
       <c r="AB6">
-        <v>27.45553485867956</v>
+        <v>35.299973389730923</v>
       </c>
       <c r="AC6">
-        <v>30.843170717373326</v>
+        <v>20.562113811582275</v>
       </c>
       <c r="AD6">
-        <v>1.4336145814080854</v>
+        <v>1.4385966152171854</v>
       </c>
       <c r="AE6">
-        <v>0.20086912366835222</v>
+        <v>0.20076189192008617</v>
       </c>
       <c r="AF6">
-        <v>16.975162558557741</v>
+        <v>26.711993486847092</v>
       </c>
       <c r="AG6">
-        <v>10.241999545672483</v>
+        <v>3.6952832192721137</v>
       </c>
       <c r="AH6">
-        <v>1114.7200192737764</v>
+        <v>1433.2145247159835</v>
       </c>
       <c r="AI6">
-        <v>8808.00024538548</v>
+        <v>5872.0001251068807</v>
       </c>
       <c r="AJ6">
-        <v>-5.1744857141339571E-15</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <v>0</v>
       </c>
       <c r="AL6">
-        <v>1131.6951818323341</v>
+        <v>1459.9265182028305</v>
       </c>
       <c r="AM6">
-        <v>8818.2422449311525</v>
+        <v>5875.6954083261544</v>
       </c>
       <c r="AN6">
-        <v>82.1649834353701</v>
+        <v>105.99571343122054</v>
       </c>
       <c r="AO6">
-        <v>312.06940018941623</v>
+        <v>207.93540150544661</v>
       </c>
       <c r="AP6">
         <v>8.70021070939704</v>
@@ -1351,40 +1351,40 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D7">
-        <v>26.148430245992834</v>
+        <v>26.361361914675783</v>
       </c>
       <c r="E7">
-        <v>25.139258064668752</v>
+        <v>25.0848411492262</v>
       </c>
       <c r="F7">
-        <v>48.107043535728224</v>
+        <v>48.0560469180964</v>
       </c>
       <c r="G7">
-        <v>47.983839480702187</v>
+        <v>47.973482611880748</v>
       </c>
       <c r="H7">
-        <v>31.406276844739608</v>
+        <v>40.379498800379494</v>
       </c>
       <c r="I7">
-        <v>50.473070239288788</v>
+        <v>33.648713492859187</v>
       </c>
       <c r="J7">
-        <v>64.044649555041445</v>
+        <v>82.343120856481818</v>
       </c>
       <c r="K7">
-        <v>27.314093374434588</v>
+        <v>18.209395582956393</v>
       </c>
       <c r="L7">
-        <v>351.30581675226841</v>
+        <v>451.67890725291647</v>
       </c>
       <c r="M7">
-        <v>1093.2982082906203</v>
+        <v>728.86547219374677</v>
       </c>
       <c r="N7">
         <v>11.185847290622426</v>
@@ -1393,64 +1393,64 @@
         <v>21.661020482950232</v>
       </c>
       <c r="P7">
-        <v>2.0392308795994256</v>
+        <v>2.0392308795994252</v>
       </c>
       <c r="Q7">
-        <v>0.541161717425563</v>
+        <v>0.54116171742556307</v>
       </c>
       <c r="R7">
-        <v>148.85113803545022</v>
+        <v>196.19950362636914</v>
       </c>
       <c r="S7">
-        <v>22.609622931678196</v>
+        <v>12.719947124013164</v>
       </c>
       <c r="T7">
-        <v>5027.6502185543923</v>
+        <v>6464.1217095699312</v>
       </c>
       <c r="U7">
-        <v>30297.907287509246</v>
+        <v>20198.604858339491</v>
       </c>
       <c r="V7">
-        <v>744.41579399698094</v>
+        <v>957.10602085326127</v>
       </c>
       <c r="W7">
-        <v>615.253939630881</v>
+        <v>410.16929308725389</v>
       </c>
       <c r="X7">
-        <v>18.249310989686141</v>
+        <v>28.282868853243983</v>
       </c>
       <c r="Y7">
-        <v>7.82828125124698</v>
+        <v>2.86571933705902</v>
       </c>
       <c r="Z7">
-        <v>1097.9970000561327</v>
+        <v>1411.7104286435988</v>
       </c>
       <c r="AA7">
-        <v>6615.9524037533256</v>
+        <v>4410.6349358355483</v>
       </c>
       <c r="AB7">
-        <v>28.022124292858173</v>
+        <v>36.028445519389379</v>
       </c>
       <c r="AC7">
-        <v>23.602803574038077</v>
+        <v>15.735202382691909</v>
       </c>
       <c r="AD7">
-        <v>1.485634049352915</v>
+        <v>1.4908002543296484</v>
       </c>
       <c r="AE7">
-        <v>0.20464476778976717</v>
+        <v>0.20453551970113268</v>
       </c>
       <c r="AF7">
-        <v>17.522556687718218</v>
+        <v>27.345219685131617</v>
       </c>
       <c r="AG7">
-        <v>7.7439781692803438</v>
+        <v>2.8095472857188177</v>
       </c>
       <c r="AH7">
-        <v>1098.7237543581007</v>
+        <v>1412.6480778117116</v>
       </c>
       <c r="AI7">
-        <v>6616.0367068352925</v>
+        <v>4410.6911078868889</v>
       </c>
       <c r="AJ7">
         <v>0</v>
@@ -1459,16 +1459,16 @@
         <v>0</v>
       </c>
       <c r="AL7">
-        <v>1116.2463110458189</v>
+        <v>1439.9932974968431</v>
       </c>
       <c r="AM7">
-        <v>6623.7806850045727</v>
+        <v>4413.5006551726074</v>
       </c>
       <c r="AN7">
-        <v>81.274990940706545</v>
+        <v>104.84732719885339</v>
       </c>
       <c r="AO7">
-        <v>251.79183835247949</v>
+        <v>167.77177512105632</v>
       </c>
       <c r="AP7">
         <v>8.6687315639390512</v>
@@ -1488,40 +1488,40 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="C8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D8">
-        <v>26.616235839390249</v>
+        <v>26.832055552301913</v>
       </c>
       <c r="E8">
-        <v>25.59810248305121</v>
+        <v>25.544280194064374</v>
       </c>
       <c r="F8">
-        <v>45.371288158693254</v>
+        <v>45.32371824620671</v>
       </c>
       <c r="G8">
-        <v>45.258330694202577</v>
+        <v>45.248018851449295</v>
       </c>
       <c r="H8">
-        <v>32.589049831481809</v>
+        <v>41.90020692619089</v>
       </c>
       <c r="I8">
-        <v>44.90175169639992</v>
+        <v>29.934501130933274</v>
       </c>
       <c r="J8">
-        <v>66.987498057083783</v>
+        <v>86.126783216250544</v>
       </c>
       <c r="K8">
-        <v>22.278478442797923</v>
+        <v>14.852318961865279</v>
       </c>
       <c r="L8">
-        <v>371.33698439059526</v>
+        <v>477.433265645051</v>
       </c>
       <c r="M8">
-        <v>917.36882469588</v>
+        <v>611.57921646391992</v>
       </c>
       <c r="N8">
         <v>11.394532406154251</v>
@@ -1530,82 +1530,82 @@
         <v>20.430579878010235</v>
       </c>
       <c r="P8">
-        <v>2.0555216676606585</v>
+        <v>2.055521667660658</v>
       </c>
       <c r="Q8">
         <v>0.49616056392259061</v>
       </c>
       <c r="R8">
-        <v>157.07433689288013</v>
+        <v>207.14202962568331</v>
       </c>
       <c r="S8">
-        <v>17.184897989589324</v>
+        <v>9.5942802633209254</v>
       </c>
       <c r="T8">
-        <v>5413.4676129507425</v>
+        <v>6960.1726452223811</v>
       </c>
       <c r="U8">
-        <v>23978.375307795068</v>
+        <v>15985.583538530043</v>
       </c>
       <c r="V8">
-        <v>793.159141776565</v>
+        <v>1019.7760394270119</v>
       </c>
       <c r="W8">
-        <v>473.32041543989521</v>
+        <v>315.54694362659671</v>
       </c>
       <c r="X8">
-        <v>19.380083174168181</v>
+        <v>30.106560558768031</v>
       </c>
       <c r="Y8">
-        <v>6.131195562073426</v>
+        <v>2.2251453116436632</v>
       </c>
       <c r="Z8">
-        <v>1182.2563107085093</v>
+        <v>1520.0438280537969</v>
       </c>
       <c r="AA8">
-        <v>5235.9982572495283</v>
+        <v>3490.6655048330176</v>
       </c>
       <c r="AB8">
-        <v>29.867924357928739</v>
+        <v>38.40161703162287</v>
       </c>
       <c r="AC8">
-        <v>18.158182053783229</v>
+        <v>12.105454702522133</v>
       </c>
       <c r="AD8">
-        <v>1.4703225448573825</v>
+        <v>1.4754345042512735</v>
       </c>
       <c r="AE8">
-        <v>0.19892866514192378</v>
+        <v>0.19882246965761119</v>
       </c>
       <c r="AF8">
-        <v>18.613445117226497</v>
+        <v>29.117454579505626</v>
       </c>
       <c r="AG8">
-        <v>6.0681508236565165</v>
+        <v>2.1831379232891024</v>
       </c>
       <c r="AH8">
-        <v>1183.0229487654513</v>
+        <v>1521.0329340330593</v>
       </c>
       <c r="AI8">
-        <v>5236.0613019879456</v>
+        <v>3490.7075122213723</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>-5.4913713720406992E-15</v>
       </c>
       <c r="AK8">
-        <v>3.54729718627758E-15</v>
+        <v>1.77364859313879E-15</v>
       </c>
       <c r="AL8">
-        <v>1201.6363938826776</v>
+        <v>1550.1503886125649</v>
       </c>
       <c r="AM8">
-        <v>5242.1294528116014</v>
+        <v>3492.8906501446613</v>
       </c>
       <c r="AN8">
-        <v>85.909681024916253</v>
+        <v>110.82630827787484</v>
       </c>
       <c r="AO8">
-        <v>211.27432780301692</v>
+        <v>140.77449457165812</v>
       </c>
       <c r="AP8">
         <v>8.830456930014055</v>
@@ -1625,40 +1625,40 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>27.782988158907116</v>
+        <v>27.994630064061404</v>
       </c>
       <c r="E9">
-        <v>26.852370147830189</v>
+        <v>26.818484536200234</v>
       </c>
       <c r="F9">
-        <v>43.560521068315047</v>
+        <v>43.517388121595118</v>
       </c>
       <c r="G9">
-        <v>43.467671877156633</v>
+        <v>43.45515584513835</v>
       </c>
       <c r="H9">
-        <v>36.202163938314875</v>
+        <v>46.545639349261982</v>
       </c>
       <c r="I9">
-        <v>41.41613193467871</v>
+        <v>27.610754623119135</v>
       </c>
       <c r="J9">
-        <v>67.267255201485753</v>
+        <v>86.492042365156209</v>
       </c>
       <c r="K9">
-        <v>16.893502481894593</v>
+        <v>11.262334987929725</v>
       </c>
       <c r="L9">
-        <v>434.77288868388092</v>
+        <v>558.99371402213251</v>
       </c>
       <c r="M9">
-        <v>812.64965355238587</v>
+        <v>541.76643570159047</v>
       </c>
       <c r="N9">
         <v>12.009582891914787</v>
@@ -1667,82 +1667,82 @@
         <v>19.621572937668159</v>
       </c>
       <c r="P9">
-        <v>1.8581003974265979</v>
+        <v>1.8582200948224295</v>
       </c>
       <c r="Q9">
-        <v>0.40789667438134808</v>
+        <v>0.407896674381348</v>
       </c>
       <c r="R9">
-        <v>144.74008553325683</v>
+        <v>192.49816006513282</v>
       </c>
       <c r="S9">
-        <v>11.857849119468481</v>
+        <v>6.3198567218132364</v>
       </c>
       <c r="T9">
-        <v>6680.3806227841023</v>
+        <v>8589.0608007224182</v>
       </c>
       <c r="U9">
-        <v>20400.098130927832</v>
+        <v>13600.065420618552</v>
       </c>
       <c r="V9">
-        <v>839.6674194043494</v>
+        <v>1079.5723963770204</v>
       </c>
       <c r="W9">
-        <v>344.702146837974</v>
+        <v>229.80143122531592</v>
       </c>
       <c r="X9">
-        <v>19.750771909579818</v>
+        <v>31.776908899966688</v>
       </c>
       <c r="Y9">
-        <v>4.9670456384506272</v>
+        <v>1.725987734468003</v>
       </c>
       <c r="Z9">
-        <v>1458.9395769777943</v>
+        <v>1875.7794561143078</v>
       </c>
       <c r="AA9">
-        <v>4454.6336809789318</v>
+        <v>2969.7557873192873</v>
       </c>
       <c r="AB9">
-        <v>31.815742150520173</v>
+        <v>40.83904410167149</v>
       </c>
       <c r="AC9">
-        <v>13.225055716801199</v>
+        <v>8.8167038112007834</v>
       </c>
       <c r="AD9">
-        <v>1.2657973077624807</v>
+        <v>1.268098251500243</v>
       </c>
       <c r="AE9">
-        <v>0.17028937533427294</v>
+        <v>0.17019841723856033</v>
       </c>
       <c r="AF9">
-        <v>19.047773638292544</v>
+        <v>30.872891560995335</v>
       </c>
       <c r="AG9">
-        <v>4.9277391986541765</v>
+        <v>1.6997974380721614</v>
       </c>
       <c r="AH9">
-        <v>1459.6425752490816</v>
+        <v>1876.683473453279</v>
       </c>
       <c r="AI9">
-        <v>4454.6729874187295</v>
+        <v>2969.7819776156821</v>
       </c>
       <c r="AJ9">
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>3.0179363601879143E-15</v>
+        <v>-1.5089681800939572E-15</v>
       </c>
       <c r="AL9">
-        <v>1478.6903488873741</v>
+        <v>1907.5563650142744</v>
       </c>
       <c r="AM9">
-        <v>4459.6007266173829</v>
+        <v>2971.481775053755</v>
       </c>
       <c r="AN9">
-        <v>100.59083741462813</v>
+        <v>129.76516335388061</v>
       </c>
       <c r="AO9">
-        <v>187.15655681538459</v>
+        <v>124.70450422599951</v>
       </c>
       <c r="AP9">
         <v>9.3071045563229013</v>
@@ -1762,124 +1762,124 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>30.129241090593958</v>
+        <v>30.34718590431212</v>
       </c>
       <c r="E10">
-        <v>29.22897523195336</v>
+        <v>29.209927394710725</v>
       </c>
       <c r="F10">
-        <v>42.792733933219765</v>
+        <v>42.752270416010248</v>
       </c>
       <c r="G10">
-        <v>42.713233872541956</v>
+        <v>42.698978000871726</v>
       </c>
       <c r="H10">
-        <v>43.127311408876366</v>
+        <v>55.449400382841034</v>
       </c>
       <c r="I10">
-        <v>39.98765244367096</v>
+        <v>26.658434962447302</v>
       </c>
       <c r="J10">
-        <v>76.984865991656633</v>
+        <v>98.986935663877588</v>
       </c>
       <c r="K10">
-        <v>13.969156160593098</v>
+        <v>9.3127707737287277</v>
       </c>
       <c r="L10">
-        <v>565.31334252189413</v>
+        <v>726.83144038529224</v>
       </c>
       <c r="M10">
-        <v>770.97077287503043</v>
+        <v>513.98051525002006</v>
       </c>
       <c r="N10">
         <v>13.108012627134054</v>
       </c>
       <c r="O10">
-        <v>19.280220912219509</v>
+        <v>19.280220912219505</v>
       </c>
       <c r="P10">
-        <v>1.7850606373717</v>
+        <v>1.7851759438413937</v>
       </c>
       <c r="Q10">
-        <v>0.34933674039182222</v>
+        <v>0.34933674039182211</v>
       </c>
       <c r="R10">
-        <v>161.6633016800335</v>
+        <v>216.94087365203333</v>
       </c>
       <c r="S10">
-        <v>9.3561021703729814</v>
+        <v>4.7596054726749548</v>
       </c>
       <c r="T10">
-        <v>9480.6238427123</v>
+        <v>12189.373512058673</v>
       </c>
       <c r="U10">
-        <v>19017.131216389058</v>
+        <v>12678.087477592704</v>
       </c>
       <c r="V10">
-        <v>1048.97914849381</v>
+        <v>1348.6874766348985</v>
       </c>
       <c r="W10">
-        <v>280.0745223587806</v>
+        <v>186.71634823918706</v>
       </c>
       <c r="X10">
-        <v>24.240647724991987</v>
+        <v>40.231777350303375</v>
       </c>
       <c r="Y10">
-        <v>4.4761626912070458</v>
+        <v>1.5063124865643345</v>
       </c>
       <c r="Z10">
-        <v>2070.4894106479551</v>
+        <v>2662.0578136902295</v>
       </c>
       <c r="AA10">
-        <v>4152.6443984938614</v>
+        <v>2768.4295989959096</v>
       </c>
       <c r="AB10">
-        <v>39.860552976951638</v>
+        <v>51.1654740314848</v>
       </c>
       <c r="AC10">
-        <v>10.746105625253557</v>
+        <v>7.1640704168358029</v>
       </c>
       <c r="AD10">
-        <v>1.1155471588685226</v>
+        <v>1.1175716522209696</v>
       </c>
       <c r="AE10">
-        <v>0.14842719828313675</v>
+        <v>0.14834792568639738</v>
       </c>
       <c r="AF10">
-        <v>23.464465838368149</v>
+        <v>39.233652591619595</v>
       </c>
       <c r="AG10">
-        <v>4.4483243769022689</v>
+        <v>1.4877635224049202</v>
       </c>
       <c r="AH10">
-        <v>2071.2655925345794</v>
+        <v>2663.0559384489129</v>
       </c>
       <c r="AI10">
-        <v>4152.6722368081655</v>
+        <v>2768.4481479600695</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>-9.6170569552145811E-15</v>
       </c>
       <c r="AK10">
-        <v>-1.4066719531460129E-15</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2094.7300583729475</v>
+        <v>2702.2895910405327</v>
       </c>
       <c r="AM10">
-        <v>4157.1205611850673</v>
+        <v>2769.9359114824738</v>
       </c>
       <c r="AN10">
-        <v>130.79263511265259</v>
+        <v>168.7278470135584</v>
       </c>
       <c r="AO10">
-        <v>177.55740721643829</v>
+        <v>118.3084857318466</v>
       </c>
       <c r="AP10">
         <v>10.158358133192948</v>
@@ -1899,10 +1899,10 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="C11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11">
         <v>27.011982828585488</v>
@@ -1911,94 +1911,94 @@
         <v>26.685686374384805</v>
       </c>
       <c r="F11">
-        <v>33.357713128789925</v>
+        <v>33.277496345364987</v>
       </c>
       <c r="G11">
-        <v>32.82832037147729</v>
+        <v>32.779357296831833</v>
       </c>
       <c r="H11">
         <v>15.355359401901744</v>
       </c>
       <c r="I11">
-        <v>92.685617642291348</v>
+        <v>86.506576466138611</v>
       </c>
       <c r="J11">
         <v>22.456494173976129</v>
       </c>
       <c r="K11">
-        <v>58.340035716307185</v>
+        <v>54.450700001886723</v>
       </c>
       <c r="L11">
         <v>183.45900345922203</v>
       </c>
       <c r="M11">
-        <v>1360.3090212836589</v>
+        <v>1269.6217531980813</v>
       </c>
       <c r="N11">
         <v>11.947555160219878</v>
       </c>
       <c r="O11">
-        <v>14.676592290009902</v>
+        <v>14.676592290009896</v>
       </c>
       <c r="P11">
         <v>1.4624531791287747</v>
       </c>
       <c r="Q11">
-        <v>0.62944000590753268</v>
+        <v>0.6294400059075328</v>
       </c>
       <c r="R11">
         <v>36.649867288142907</v>
       </c>
       <c r="S11">
-        <v>126.09798482100753</v>
+        <v>107.38034955982919</v>
       </c>
       <c r="T11">
         <v>2804.2269403293008</v>
       </c>
       <c r="U11">
-        <v>25543.101956070077</v>
+        <v>23840.228492332069</v>
       </c>
       <c r="V11">
         <v>278.91899731086585</v>
       </c>
       <c r="W11">
-        <v>890.36777505259147</v>
+        <v>831.00992338241872</v>
       </c>
       <c r="X11">
         <v>3.8082959913247088</v>
       </c>
       <c r="Y11">
-        <v>89.376432395089438</v>
+        <v>73.106900628972312</v>
       </c>
       <c r="Z11">
         <v>612.34037686127635</v>
       </c>
       <c r="AA11">
-        <v>5578.4010622674168</v>
+        <v>5206.5076581162612</v>
       </c>
       <c r="AB11">
         <v>10.618794462129781</v>
       </c>
       <c r="AC11">
-        <v>34.134856659735135</v>
+        <v>31.859199549086092</v>
       </c>
       <c r="AD11">
         <v>0.99939722577395429</v>
       </c>
       <c r="AE11">
-        <v>0.35628959871558818</v>
+        <v>0.35557401829824742</v>
       </c>
       <c r="AF11">
         <v>3.6230559924562384</v>
       </c>
       <c r="AG11">
-        <v>89.164164558795662</v>
+        <v>72.90918189412973</v>
       </c>
       <c r="AH11">
         <v>612.52561686014462</v>
       </c>
       <c r="AI11">
-        <v>5578.6133301037116</v>
+        <v>5206.7053768511023</v>
       </c>
       <c r="AJ11">
         <v>1.6593995560458396E-15</v>
@@ -2010,13 +2010,13 @@
         <v>616.148672852601</v>
       </c>
       <c r="AM11">
-        <v>5667.7774946625059</v>
+        <v>5279.6145587452338</v>
       </c>
       <c r="AN11">
         <v>42.258812489328747</v>
       </c>
       <c r="AO11">
-        <v>317.85083027466692</v>
+        <v>296.08252487112094</v>
       </c>
       <c r="AP11">
         <v>9.2590347282970846</v>
@@ -2500,106 +2500,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>28.118206703540103</v>
+        <v>28.321637242839358</v>
       </c>
       <c r="E3">
-        <v>27.277725087198327</v>
+        <v>27.259899548519414</v>
       </c>
       <c r="F3">
-        <v>70.739604742402236</v>
+        <v>70.6493051746511</v>
       </c>
       <c r="G3">
-        <v>70.628464807371074</v>
+        <v>70.586764589953845</v>
       </c>
       <c r="H3">
-        <v>37.560841960432178</v>
+        <v>48.292511091984224</v>
       </c>
       <c r="I3">
-        <v>109.32280890054773</v>
+        <v>69.814217961473943</v>
       </c>
       <c r="J3">
-        <v>62.597088467412078</v>
+        <v>80.487169601993415</v>
       </c>
       <c r="K3">
-        <v>53.412476074859008</v>
+        <v>34.980616976303814</v>
       </c>
       <c r="L3">
-        <v>459.47685198649066</v>
+        <v>590.75595255405938</v>
       </c>
       <c r="M3">
-        <v>3485.0998389755068</v>
+        <v>2463.9786960211127</v>
       </c>
       <c r="N3">
-        <v>12.232868807108174</v>
+        <v>12.232868807108176</v>
       </c>
       <c r="O3">
-        <v>31.878981833936816</v>
+        <v>35.29336527669517</v>
       </c>
       <c r="P3">
-        <v>1.6665517917131332</v>
+        <v>1.6666594422619077</v>
       </c>
       <c r="Q3">
-        <v>0.48857577491856247</v>
+        <v>0.50105290867266339</v>
       </c>
       <c r="R3">
-        <v>122.71624921467101</v>
+        <v>164.67148931400143</v>
       </c>
       <c r="S3">
-        <v>58.515565830312774</v>
+        <v>27.082850896314437</v>
       </c>
       <c r="T3">
-        <v>7191.2234535267562</v>
+        <v>9245.8587259629712</v>
       </c>
       <c r="U3">
-        <v>142139.48878733968</v>
+        <v>105910.79076673692</v>
       </c>
       <c r="V3">
-        <v>795.98880992712134</v>
+        <v>1023.4141841920133</v>
       </c>
       <c r="W3">
-        <v>1770.6773829845913</v>
+        <v>1234.5836925488545</v>
       </c>
       <c r="X3">
-        <v>18.394959273279884</v>
+        <v>30.526788115903535</v>
       </c>
       <c r="Y3">
-        <v>32.419523941719355</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="Z3">
-        <v>1570.5034032729534</v>
+        <v>2019.21866135094</v>
       </c>
       <c r="AA3">
-        <v>31038.054331183379</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AB3">
-        <v>30.246838998325174</v>
+        <v>38.825197795362634</v>
       </c>
       <c r="AC3">
-        <v>67.9420284885761</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.1159912849093541</v>
+        <v>1.1180165935167421</v>
       </c>
       <c r="AE3">
-        <v>0.1255502938646294</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.805745227229156</v>
+        <v>29.769093119297569</v>
       </c>
       <c r="AG3">
-        <v>32.270644646107591</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="AH3">
-        <v>1571.0926173190044</v>
+        <v>2019.9763563475462</v>
       </c>
       <c r="AI3">
-        <v>31038.203210478991</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -2608,16 +2608,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>1588.8983625462336</v>
+        <v>2049.7454494668432</v>
       </c>
       <c r="AM3">
-        <v>31070.4738551251</v>
+        <v>18958.246325081931</v>
       </c>
       <c r="AN3">
-        <v>106.30598317008956</v>
+        <v>137.13906149937242</v>
       </c>
       <c r="AO3">
-        <v>802.62996732164311</v>
+        <v>537.10763923259367</v>
       </c>
       <c r="AP3">
         <v>9.4801451504353054</v>
@@ -2637,124 +2637,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>28.018713250709638</v>
+        <v>28.229825711877151</v>
       </c>
       <c r="E4">
-        <v>27.102296834965461</v>
+        <v>27.071761041418288</v>
       </c>
       <c r="F4">
-        <v>63.79637077054727</v>
+        <v>63.732492283173976</v>
       </c>
       <c r="G4">
-        <v>63.656039358054585</v>
+        <v>63.638437772222545</v>
       </c>
       <c r="H4">
-        <v>36.927401065004595</v>
+        <v>47.478087083577321</v>
       </c>
       <c r="I4">
-        <v>88.8225275127105</v>
+        <v>59.215018341806989</v>
       </c>
       <c r="J4">
-        <v>67.458484450728932</v>
+        <v>86.73792793371706</v>
       </c>
       <c r="K4">
-        <v>54.756061318240157</v>
+        <v>36.504040878826764</v>
       </c>
       <c r="L4">
-        <v>447.90279610402382</v>
+        <v>575.87502356231641</v>
       </c>
       <c r="M4">
-        <v>2552.3118811767781</v>
+        <v>1701.5412541178519</v>
       </c>
       <c r="N4">
-        <v>12.129280241400279</v>
+        <v>12.129280241400281</v>
       </c>
       <c r="O4">
         <v>28.734961193392547</v>
       </c>
       <c r="P4">
-        <v>1.8267866815750018</v>
+        <v>1.8269044365883842</v>
       </c>
       <c r="Q4">
-        <v>0.61646592200840689</v>
+        <v>0.61646592200840677</v>
       </c>
       <c r="R4">
-        <v>143.13929937715912</v>
+        <v>190.69914932802081</v>
       </c>
       <c r="S4">
-        <v>56.806794491279014</v>
+        <v>30.579178240351204</v>
       </c>
       <c r="T4">
-        <v>6950.7174204389657</v>
+        <v>8936.6366834215278</v>
       </c>
       <c r="U4">
-        <v>93829.508196535928</v>
+        <v>62553.005464357258</v>
       </c>
       <c r="V4">
-        <v>850.46933396312443</v>
+        <v>1093.4605722383028</v>
       </c>
       <c r="W4">
-        <v>1636.1873341296166</v>
+        <v>1090.7915560864108</v>
       </c>
       <c r="X4">
-        <v>19.907038423333169</v>
+        <v>32.23724396542957</v>
       </c>
       <c r="Y4">
-        <v>23.051548665181226</v>
+        <v>8.0756810229526952</v>
       </c>
       <c r="Z4">
-        <v>1517.9788855864927</v>
+        <v>1951.687138611203</v>
       </c>
       <c r="AA4">
-        <v>20488.925337486471</v>
+        <v>13659.283558324305</v>
       </c>
       <c r="AB4">
-        <v>32.246471400090151</v>
+        <v>41.391936771866753</v>
       </c>
       <c r="AC4">
-        <v>62.774037046962746</v>
+        <v>41.849358031308576</v>
       </c>
       <c r="AD4">
-        <v>1.2325487418079597</v>
+        <v>1.2347883954903314</v>
       </c>
       <c r="AE4">
-        <v>0.17573851509306887</v>
+        <v>0.17564464381670725</v>
       </c>
       <c r="AF4">
-        <v>19.213244217584567</v>
+        <v>31.34506311307711</v>
       </c>
       <c r="AG4">
-        <v>22.859006548711257</v>
+        <v>7.9473881770507271</v>
       </c>
       <c r="AH4">
-        <v>1518.6726797922415</v>
+        <v>1952.5793194635558</v>
       </c>
       <c r="AI4">
-        <v>20489.117879602942</v>
+        <v>13659.411851170204</v>
       </c>
       <c r="AJ4">
-        <v>-7.0507433288103095E-15</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>-6.9404441740299753E-15</v>
       </c>
       <c r="AL4">
-        <v>1537.8859240098261</v>
+        <v>1983.9243825766325</v>
       </c>
       <c r="AM4">
-        <v>20511.976886151653</v>
+        <v>13667.359239347255</v>
       </c>
       <c r="AN4">
-        <v>103.62870921633811</v>
+        <v>133.68437731548397</v>
       </c>
       <c r="AO4">
-        <v>587.8082179034426</v>
+        <v>391.66317915221271</v>
       </c>
       <c r="AP4">
         <v>9.39986679101518</v>
@@ -2774,43 +2774,43 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D5">
-        <v>26.976058898859058</v>
+        <v>27.191154191894135</v>
       </c>
       <c r="E5">
-        <v>25.979886567667421</v>
+        <v>25.931469876663538</v>
       </c>
       <c r="F5">
-        <v>56.557931208200259</v>
+        <v>56.498569826328939</v>
       </c>
       <c r="G5">
-        <v>56.416737256794427</v>
+        <v>56.403947728372586</v>
       </c>
       <c r="H5">
-        <v>33.666766708926517</v>
+        <v>43.285842911476941</v>
       </c>
       <c r="I5">
-        <v>69.7722169687325</v>
+        <v>46.514811312488327</v>
       </c>
       <c r="J5">
-        <v>67.486716865014117</v>
+        <v>86.768635969303872</v>
       </c>
       <c r="K5">
-        <v>43.271836046223775</v>
+        <v>28.847890697482509</v>
       </c>
       <c r="L5">
-        <v>389.90856301663251</v>
+        <v>501.31100959281304</v>
       </c>
       <c r="M5">
-        <v>1776.9402929832165</v>
+        <v>1184.6268619888108</v>
       </c>
       <c r="N5">
-        <v>11.581408051081152</v>
+        <v>11.58140805108115</v>
       </c>
       <c r="O5">
         <v>25.467734439046545</v>
@@ -2822,58 +2822,58 @@
         <v>0.62018720238767078</v>
       </c>
       <c r="R5">
-        <v>154.8850352594369</v>
+        <v>204.67610842602153</v>
       </c>
       <c r="S5">
-        <v>41.655430021181168</v>
+        <v>23.273602248626645</v>
       </c>
       <c r="T5">
-        <v>5777.4336340439813</v>
+        <v>7428.1289580565453</v>
       </c>
       <c r="U5">
-        <v>57897.2892944596</v>
+        <v>38598.192862973061</v>
       </c>
       <c r="V5">
-        <v>812.218751320501</v>
+        <v>1044.2812516977867</v>
       </c>
       <c r="W5">
-        <v>1146.0000141920996</v>
+        <v>764.00000946139971</v>
       </c>
       <c r="X5">
-        <v>19.604537651955095</v>
+        <v>30.744040073544944</v>
       </c>
       <c r="Y5">
-        <v>14.818791081495675</v>
+        <v>5.3825096221696533</v>
       </c>
       <c r="Z5">
-        <v>1261.7434631376714</v>
+        <v>1622.2415954627224</v>
       </c>
       <c r="AA5">
-        <v>12642.64579872148</v>
+        <v>8428.4305324809848</v>
       </c>
       <c r="AB5">
-        <v>30.627545278992272</v>
+        <v>39.378272501561611</v>
       </c>
       <c r="AC5">
-        <v>43.964385076910709</v>
+        <v>29.309590051273762</v>
       </c>
       <c r="AD5">
-        <v>1.41160428996194</v>
+        <v>1.4165085019227341</v>
       </c>
       <c r="AE5">
-        <v>0.19947477922290915</v>
+        <v>0.19936829209814289</v>
       </c>
       <c r="AF5">
-        <v>18.849809741603625</v>
+        <v>29.770302994238737</v>
       </c>
       <c r="AG5">
-        <v>14.665728822568124</v>
+        <v>5.2805225902439483</v>
       </c>
       <c r="AH5">
-        <v>1262.4981910480231</v>
+        <v>1623.2153325420291</v>
       </c>
       <c r="AI5">
-        <v>12642.798860980411</v>
+        <v>8428.53251951291</v>
       </c>
       <c r="AJ5">
         <v>5.8605751304312572E-15</v>
@@ -2882,16 +2882,16 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>1281.3480007896264</v>
+        <v>1652.9856355362676</v>
       </c>
       <c r="AM5">
-        <v>12657.464589802978</v>
+        <v>8433.8130421031528</v>
       </c>
       <c r="AN5">
-        <v>90.207792954583979</v>
+        <v>116.37134164603774</v>
       </c>
       <c r="AO5">
-        <v>409.23767750384673</v>
+        <v>272.67973276673973</v>
       </c>
       <c r="AP5">
         <v>8.9752805414598669</v>
@@ -2911,43 +2911,43 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D6">
-        <v>26.176934098656247</v>
+        <v>26.386993270422963</v>
       </c>
       <c r="E6">
-        <v>25.197208770838049</v>
+        <v>25.147980550060186</v>
       </c>
       <c r="F6">
-        <v>51.67246136267908</v>
+        <v>51.618081281948413</v>
       </c>
       <c r="G6">
-        <v>51.542563493307036</v>
+        <v>51.53102983393552</v>
       </c>
       <c r="H6">
-        <v>31.634784972071781</v>
+        <v>40.673294964092285</v>
       </c>
       <c r="I6">
-        <v>58.237071832669386</v>
+        <v>38.824714555112919</v>
       </c>
       <c r="J6">
-        <v>62.442851639252481</v>
+        <v>80.283666393324609</v>
       </c>
       <c r="K6">
-        <v>33.2282012062035</v>
+        <v>22.152134137468991</v>
       </c>
       <c r="L6">
-        <v>355.14686792490596</v>
+        <v>456.61740161773605</v>
       </c>
       <c r="M6">
-        <v>1355.0282421108079</v>
+        <v>903.35216140720513</v>
       </c>
       <c r="N6">
-        <v>11.226466948912126</v>
+        <v>11.226466948912124</v>
       </c>
       <c r="O6">
         <v>23.267451461230138</v>
@@ -2956,79 +2956,79 @@
         <v>1.9738667955030851</v>
       </c>
       <c r="Q6">
-        <v>0.57056785584407421</v>
+        <v>0.570567855844074</v>
       </c>
       <c r="R6">
-        <v>140.91615045249043</v>
+        <v>186.06776357160138</v>
       </c>
       <c r="S6">
-        <v>29.309074342817961</v>
+        <v>16.406627933932498</v>
       </c>
       <c r="T6">
-        <v>5101.0774776157059</v>
+        <v>6558.5281855059075</v>
       </c>
       <c r="U6">
-        <v>40335.945966013336</v>
+        <v>26890.630644008892</v>
       </c>
       <c r="V6">
-        <v>728.46814498257083</v>
+        <v>936.60190069187684</v>
       </c>
       <c r="W6">
-        <v>803.9787294267021</v>
+        <v>535.98581961780121</v>
       </c>
       <c r="X6">
-        <v>17.662278985244562</v>
+        <v>27.598500256571025</v>
       </c>
       <c r="Y6">
-        <v>10.350130827038949</v>
+        <v>3.7673322567464971</v>
       </c>
       <c r="Z6">
-        <v>1114.0329028470894</v>
+        <v>1432.3280179462595</v>
       </c>
       <c r="AA6">
-        <v>8807.8921141041137</v>
+        <v>5871.9280760694064</v>
       </c>
       <c r="AB6">
-        <v>27.45553485867956</v>
+        <v>35.299973389730923</v>
       </c>
       <c r="AC6">
-        <v>30.843170717373326</v>
+        <v>20.562113811582275</v>
       </c>
       <c r="AD6">
-        <v>1.4336145814080854</v>
+        <v>1.4385966152171854</v>
       </c>
       <c r="AE6">
-        <v>0.20086912366835222</v>
+        <v>0.20076189192008617</v>
       </c>
       <c r="AF6">
-        <v>16.975162558557741</v>
+        <v>26.711993486847092</v>
       </c>
       <c r="AG6">
-        <v>10.241999545672483</v>
+        <v>3.6952832192721137</v>
       </c>
       <c r="AH6">
-        <v>1114.7200192737764</v>
+        <v>1433.2145247159835</v>
       </c>
       <c r="AI6">
-        <v>8808.00024538548</v>
+        <v>5872.0001251068807</v>
       </c>
       <c r="AJ6">
-        <v>-5.1744857141339571E-15</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <v>0</v>
       </c>
       <c r="AL6">
-        <v>1131.6951818323341</v>
+        <v>1459.9265182028305</v>
       </c>
       <c r="AM6">
-        <v>8818.2422449311525</v>
+        <v>5875.6954083261544</v>
       </c>
       <c r="AN6">
-        <v>82.1649834353701</v>
+        <v>105.99571343122054</v>
       </c>
       <c r="AO6">
-        <v>312.06940018941623</v>
+        <v>207.93540150544661</v>
       </c>
       <c r="AP6">
         <v>8.70021070939704</v>
@@ -3048,40 +3048,40 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D7">
-        <v>26.148430245992834</v>
+        <v>26.361361914675783</v>
       </c>
       <c r="E7">
-        <v>25.139258064668752</v>
+        <v>25.0848411492262</v>
       </c>
       <c r="F7">
-        <v>48.107043535728224</v>
+        <v>48.0560469180964</v>
       </c>
       <c r="G7">
-        <v>47.983839480702187</v>
+        <v>47.973482611880748</v>
       </c>
       <c r="H7">
-        <v>31.406276844739608</v>
+        <v>40.379498800379494</v>
       </c>
       <c r="I7">
-        <v>50.473070239288788</v>
+        <v>33.648713492859187</v>
       </c>
       <c r="J7">
-        <v>64.044649555041445</v>
+        <v>82.343120856481818</v>
       </c>
       <c r="K7">
-        <v>27.314093374434588</v>
+        <v>18.209395582956393</v>
       </c>
       <c r="L7">
-        <v>351.30581675226841</v>
+        <v>451.67890725291647</v>
       </c>
       <c r="M7">
-        <v>1093.2982082906203</v>
+        <v>728.86547219374677</v>
       </c>
       <c r="N7">
         <v>11.185847290622426</v>
@@ -3090,64 +3090,64 @@
         <v>21.661020482950232</v>
       </c>
       <c r="P7">
-        <v>2.0392308795994256</v>
+        <v>2.0392308795994252</v>
       </c>
       <c r="Q7">
-        <v>0.541161717425563</v>
+        <v>0.54116171742556307</v>
       </c>
       <c r="R7">
-        <v>148.85113803545022</v>
+        <v>196.19950362636914</v>
       </c>
       <c r="S7">
-        <v>22.609622931678196</v>
+        <v>12.719947124013164</v>
       </c>
       <c r="T7">
-        <v>5027.6502185543923</v>
+        <v>6464.1217095699312</v>
       </c>
       <c r="U7">
-        <v>30297.907287509246</v>
+        <v>20198.604858339491</v>
       </c>
       <c r="V7">
-        <v>744.41579399698094</v>
+        <v>957.10602085326127</v>
       </c>
       <c r="W7">
-        <v>615.253939630881</v>
+        <v>410.16929308725389</v>
       </c>
       <c r="X7">
-        <v>18.249310989686141</v>
+        <v>28.282868853243983</v>
       </c>
       <c r="Y7">
-        <v>7.82828125124698</v>
+        <v>2.86571933705902</v>
       </c>
       <c r="Z7">
-        <v>1097.9970000561327</v>
+        <v>1411.7104286435988</v>
       </c>
       <c r="AA7">
-        <v>6615.9524037533256</v>
+        <v>4410.6349358355483</v>
       </c>
       <c r="AB7">
-        <v>28.022124292858173</v>
+        <v>36.028445519389379</v>
       </c>
       <c r="AC7">
-        <v>23.602803574038077</v>
+        <v>15.735202382691909</v>
       </c>
       <c r="AD7">
-        <v>1.485634049352915</v>
+        <v>1.4908002543296484</v>
       </c>
       <c r="AE7">
-        <v>0.20464476778976717</v>
+        <v>0.20453551970113268</v>
       </c>
       <c r="AF7">
-        <v>17.522556687718218</v>
+        <v>27.345219685131617</v>
       </c>
       <c r="AG7">
-        <v>7.7439781692803438</v>
+        <v>2.8095472857188177</v>
       </c>
       <c r="AH7">
-        <v>1098.7237543581007</v>
+        <v>1412.6480778117116</v>
       </c>
       <c r="AI7">
-        <v>6616.0367068352925</v>
+        <v>4410.6911078868889</v>
       </c>
       <c r="AJ7">
         <v>0</v>
@@ -3156,16 +3156,16 @@
         <v>0</v>
       </c>
       <c r="AL7">
-        <v>1116.2463110458189</v>
+        <v>1439.9932974968431</v>
       </c>
       <c r="AM7">
-        <v>6623.7806850045727</v>
+        <v>4413.5006551726074</v>
       </c>
       <c r="AN7">
-        <v>81.274990940706545</v>
+        <v>104.84732719885339</v>
       </c>
       <c r="AO7">
-        <v>251.79183835247949</v>
+        <v>167.77177512105632</v>
       </c>
       <c r="AP7">
         <v>8.6687315639390512</v>
@@ -3185,40 +3185,40 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="C8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D8">
-        <v>26.616235839390249</v>
+        <v>26.832055552301913</v>
       </c>
       <c r="E8">
-        <v>25.59810248305121</v>
+        <v>25.544280194064374</v>
       </c>
       <c r="F8">
-        <v>45.371288158693254</v>
+        <v>45.32371824620671</v>
       </c>
       <c r="G8">
-        <v>45.258330694202577</v>
+        <v>45.248018851449295</v>
       </c>
       <c r="H8">
-        <v>32.589049831481809</v>
+        <v>41.90020692619089</v>
       </c>
       <c r="I8">
-        <v>44.90175169639992</v>
+        <v>29.934501130933274</v>
       </c>
       <c r="J8">
-        <v>66.987498057083783</v>
+        <v>86.126783216250544</v>
       </c>
       <c r="K8">
-        <v>22.278478442797923</v>
+        <v>14.852318961865279</v>
       </c>
       <c r="L8">
-        <v>371.33698439059526</v>
+        <v>477.433265645051</v>
       </c>
       <c r="M8">
-        <v>917.36882469588</v>
+        <v>611.57921646391992</v>
       </c>
       <c r="N8">
         <v>11.394532406154251</v>
@@ -3227,82 +3227,82 @@
         <v>20.430579878010235</v>
       </c>
       <c r="P8">
-        <v>2.0555216676606585</v>
+        <v>2.055521667660658</v>
       </c>
       <c r="Q8">
         <v>0.49616056392259061</v>
       </c>
       <c r="R8">
-        <v>157.07433689288013</v>
+        <v>207.14202962568331</v>
       </c>
       <c r="S8">
-        <v>17.184897989589324</v>
+        <v>9.5942802633209254</v>
       </c>
       <c r="T8">
-        <v>5413.4676129507425</v>
+        <v>6960.1726452223811</v>
       </c>
       <c r="U8">
-        <v>23978.375307795068</v>
+        <v>15985.583538530043</v>
       </c>
       <c r="V8">
-        <v>793.159141776565</v>
+        <v>1019.7760394270119</v>
       </c>
       <c r="W8">
-        <v>473.32041543989521</v>
+        <v>315.54694362659671</v>
       </c>
       <c r="X8">
-        <v>19.380083174168181</v>
+        <v>30.106560558768031</v>
       </c>
       <c r="Y8">
-        <v>6.131195562073426</v>
+        <v>2.2251453116436632</v>
       </c>
       <c r="Z8">
-        <v>1182.2563107085093</v>
+        <v>1520.0438280537969</v>
       </c>
       <c r="AA8">
-        <v>5235.9982572495283</v>
+        <v>3490.6655048330176</v>
       </c>
       <c r="AB8">
-        <v>29.867924357928739</v>
+        <v>38.40161703162287</v>
       </c>
       <c r="AC8">
-        <v>18.158182053783229</v>
+        <v>12.105454702522133</v>
       </c>
       <c r="AD8">
-        <v>1.4703225448573825</v>
+        <v>1.4754345042512735</v>
       </c>
       <c r="AE8">
-        <v>0.19892866514192378</v>
+        <v>0.19882246965761119</v>
       </c>
       <c r="AF8">
-        <v>18.613445117226497</v>
+        <v>29.117454579505626</v>
       </c>
       <c r="AG8">
-        <v>6.0681508236565165</v>
+        <v>2.1831379232891024</v>
       </c>
       <c r="AH8">
-        <v>1183.0229487654513</v>
+        <v>1521.0329340330593</v>
       </c>
       <c r="AI8">
-        <v>5236.0613019879456</v>
+        <v>3490.7075122213723</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>-5.4913713720406992E-15</v>
       </c>
       <c r="AK8">
-        <v>3.54729718627758E-15</v>
+        <v>1.77364859313879E-15</v>
       </c>
       <c r="AL8">
-        <v>1201.6363938826776</v>
+        <v>1550.1503886125649</v>
       </c>
       <c r="AM8">
-        <v>5242.1294528116014</v>
+        <v>3492.8906501446613</v>
       </c>
       <c r="AN8">
-        <v>85.909681024916253</v>
+        <v>110.82630827787484</v>
       </c>
       <c r="AO8">
-        <v>211.27432780301692</v>
+        <v>140.77449457165812</v>
       </c>
       <c r="AP8">
         <v>8.830456930014055</v>
@@ -3322,40 +3322,40 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>27.782988158907116</v>
+        <v>27.994630064061404</v>
       </c>
       <c r="E9">
-        <v>26.852370147830189</v>
+        <v>26.818484536200234</v>
       </c>
       <c r="F9">
-        <v>43.560521068315047</v>
+        <v>43.517388121595118</v>
       </c>
       <c r="G9">
-        <v>43.467671877156633</v>
+        <v>43.45515584513835</v>
       </c>
       <c r="H9">
-        <v>36.202163938314875</v>
+        <v>46.545639349261982</v>
       </c>
       <c r="I9">
-        <v>41.41613193467871</v>
+        <v>27.610754623119135</v>
       </c>
       <c r="J9">
-        <v>67.267255201485753</v>
+        <v>86.492042365156209</v>
       </c>
       <c r="K9">
-        <v>16.893502481894593</v>
+        <v>11.262334987929725</v>
       </c>
       <c r="L9">
-        <v>434.77288868388092</v>
+        <v>558.99371402213251</v>
       </c>
       <c r="M9">
-        <v>812.64965355238587</v>
+        <v>541.76643570159047</v>
       </c>
       <c r="N9">
         <v>12.009582891914787</v>
@@ -3364,82 +3364,82 @@
         <v>19.621572937668159</v>
       </c>
       <c r="P9">
-        <v>1.8581003974265979</v>
+        <v>1.8582200948224295</v>
       </c>
       <c r="Q9">
-        <v>0.40789667438134808</v>
+        <v>0.407896674381348</v>
       </c>
       <c r="R9">
-        <v>144.74008553325683</v>
+        <v>192.49816006513282</v>
       </c>
       <c r="S9">
-        <v>11.857849119468481</v>
+        <v>6.3198567218132364</v>
       </c>
       <c r="T9">
-        <v>6680.3806227841023</v>
+        <v>8589.0608007224182</v>
       </c>
       <c r="U9">
-        <v>20400.098130927832</v>
+        <v>13600.065420618552</v>
       </c>
       <c r="V9">
-        <v>839.6674194043494</v>
+        <v>1079.5723963770204</v>
       </c>
       <c r="W9">
-        <v>344.702146837974</v>
+        <v>229.80143122531592</v>
       </c>
       <c r="X9">
-        <v>19.750771909579818</v>
+        <v>31.776908899966688</v>
       </c>
       <c r="Y9">
-        <v>4.9670456384506272</v>
+        <v>1.725987734468003</v>
       </c>
       <c r="Z9">
-        <v>1458.9395769777943</v>
+        <v>1875.7794561143078</v>
       </c>
       <c r="AA9">
-        <v>4454.6336809789318</v>
+        <v>2969.7557873192873</v>
       </c>
       <c r="AB9">
-        <v>31.815742150520173</v>
+        <v>40.83904410167149</v>
       </c>
       <c r="AC9">
-        <v>13.225055716801199</v>
+        <v>8.8167038112007834</v>
       </c>
       <c r="AD9">
-        <v>1.2657973077624807</v>
+        <v>1.268098251500243</v>
       </c>
       <c r="AE9">
-        <v>0.17028937533427294</v>
+        <v>0.17019841723856033</v>
       </c>
       <c r="AF9">
-        <v>19.047773638292544</v>
+        <v>30.872891560995335</v>
       </c>
       <c r="AG9">
-        <v>4.9277391986541765</v>
+        <v>1.6997974380721614</v>
       </c>
       <c r="AH9">
-        <v>1459.6425752490816</v>
+        <v>1876.683473453279</v>
       </c>
       <c r="AI9">
-        <v>4454.6729874187295</v>
+        <v>2969.7819776156821</v>
       </c>
       <c r="AJ9">
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>3.0179363601879143E-15</v>
+        <v>-1.5089681800939572E-15</v>
       </c>
       <c r="AL9">
-        <v>1478.6903488873741</v>
+        <v>1907.5563650142744</v>
       </c>
       <c r="AM9">
-        <v>4459.6007266173829</v>
+        <v>2971.481775053755</v>
       </c>
       <c r="AN9">
-        <v>100.59083741462813</v>
+        <v>129.76516335388061</v>
       </c>
       <c r="AO9">
-        <v>187.15655681538459</v>
+        <v>124.70450422599951</v>
       </c>
       <c r="AP9">
         <v>9.3071045563229013</v>
@@ -3459,124 +3459,124 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>30.129241090593958</v>
+        <v>30.34718590431212</v>
       </c>
       <c r="E10">
-        <v>29.22897523195336</v>
+        <v>29.209927394710725</v>
       </c>
       <c r="F10">
-        <v>42.792733933219765</v>
+        <v>42.752270416010248</v>
       </c>
       <c r="G10">
-        <v>42.713233872541956</v>
+        <v>42.698978000871726</v>
       </c>
       <c r="H10">
-        <v>43.127311408876366</v>
+        <v>55.449400382841034</v>
       </c>
       <c r="I10">
-        <v>39.98765244367096</v>
+        <v>26.658434962447302</v>
       </c>
       <c r="J10">
-        <v>76.984865991656633</v>
+        <v>98.986935663877588</v>
       </c>
       <c r="K10">
-        <v>13.969156160593098</v>
+        <v>9.3127707737287277</v>
       </c>
       <c r="L10">
-        <v>565.31334252189413</v>
+        <v>726.83144038529224</v>
       </c>
       <c r="M10">
-        <v>770.97077287503043</v>
+        <v>513.98051525002006</v>
       </c>
       <c r="N10">
         <v>13.108012627134054</v>
       </c>
       <c r="O10">
-        <v>19.280220912219509</v>
+        <v>19.280220912219505</v>
       </c>
       <c r="P10">
-        <v>1.7850606373717</v>
+        <v>1.7851759438413937</v>
       </c>
       <c r="Q10">
-        <v>0.34933674039182222</v>
+        <v>0.34933674039182211</v>
       </c>
       <c r="R10">
-        <v>161.6633016800335</v>
+        <v>216.94087365203333</v>
       </c>
       <c r="S10">
-        <v>9.3561021703729814</v>
+        <v>4.7596054726749548</v>
       </c>
       <c r="T10">
-        <v>9480.6238427123</v>
+        <v>12189.373512058673</v>
       </c>
       <c r="U10">
-        <v>19017.131216389058</v>
+        <v>12678.087477592704</v>
       </c>
       <c r="V10">
-        <v>1048.97914849381</v>
+        <v>1348.6874766348985</v>
       </c>
       <c r="W10">
-        <v>280.0745223587806</v>
+        <v>186.71634823918706</v>
       </c>
       <c r="X10">
-        <v>24.240647724991987</v>
+        <v>40.231777350303375</v>
       </c>
       <c r="Y10">
-        <v>4.4761626912070458</v>
+        <v>1.5063124865643345</v>
       </c>
       <c r="Z10">
-        <v>2070.4894106479551</v>
+        <v>2662.0578136902295</v>
       </c>
       <c r="AA10">
-        <v>4152.6443984938614</v>
+        <v>2768.4295989959096</v>
       </c>
       <c r="AB10">
-        <v>39.860552976951638</v>
+        <v>51.1654740314848</v>
       </c>
       <c r="AC10">
-        <v>10.746105625253557</v>
+        <v>7.1640704168358029</v>
       </c>
       <c r="AD10">
-        <v>1.1155471588685226</v>
+        <v>1.1175716522209696</v>
       </c>
       <c r="AE10">
-        <v>0.14842719828313675</v>
+        <v>0.14834792568639738</v>
       </c>
       <c r="AF10">
-        <v>23.464465838368149</v>
+        <v>39.233652591619595</v>
       </c>
       <c r="AG10">
-        <v>4.4483243769022689</v>
+        <v>1.4877635224049202</v>
       </c>
       <c r="AH10">
-        <v>2071.2655925345794</v>
+        <v>2663.0559384489129</v>
       </c>
       <c r="AI10">
-        <v>4152.6722368081655</v>
+        <v>2768.4481479600695</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>-9.6170569552145811E-15</v>
       </c>
       <c r="AK10">
-        <v>-1.4066719531460129E-15</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2094.7300583729475</v>
+        <v>2702.2895910405327</v>
       </c>
       <c r="AM10">
-        <v>4157.1205611850673</v>
+        <v>2769.9359114824738</v>
       </c>
       <c r="AN10">
-        <v>130.79263511265259</v>
+        <v>168.7278470135584</v>
       </c>
       <c r="AO10">
-        <v>177.55740721643829</v>
+        <v>118.3084857318466</v>
       </c>
       <c r="AP10">
         <v>10.158358133192948</v>
@@ -3596,124 +3596,124 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="C11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>30.032865421582176</v>
+        <v>30.127182097724692</v>
       </c>
       <c r="E11">
-        <v>29.424881221000348</v>
+        <v>29.402938552282066</v>
       </c>
       <c r="F11">
-        <v>37.816439063999155</v>
+        <v>37.738583135566721</v>
       </c>
       <c r="G11">
-        <v>37.651980850531586</v>
+        <v>37.618359427293711</v>
       </c>
       <c r="H11">
-        <v>31.221958795995924</v>
+        <v>37.4663505551951</v>
       </c>
       <c r="I11">
-        <v>51.678360279737774</v>
+        <v>37.415132842530141</v>
       </c>
       <c r="J11">
-        <v>51.699762619477816</v>
+        <v>62.039715143373378</v>
       </c>
       <c r="K11">
-        <v>22.652664575158152</v>
+        <v>16.400529152414496</v>
       </c>
       <c r="L11">
-        <v>412.01677263302179</v>
+        <v>494.42012715962613</v>
       </c>
       <c r="M11">
-        <v>877.38006901950894</v>
+        <v>635.22316997012445</v>
       </c>
       <c r="N11">
-        <v>13.19637807881103</v>
+        <v>13.196378078811032</v>
       </c>
       <c r="O11">
         <v>16.977707192530932</v>
       </c>
       <c r="P11">
-        <v>1.6558782540609873</v>
+        <v>1.6558782540609878</v>
       </c>
       <c r="Q11">
-        <v>0.4383394607053715</v>
+        <v>0.43833946070537155</v>
       </c>
       <c r="R11">
-        <v>98.046967252795653</v>
+        <v>119.79577106224403</v>
       </c>
       <c r="S11">
-        <v>22.024083897144394</v>
+        <v>12.120543761182264</v>
       </c>
       <c r="T11">
-        <v>6956.0825694862542</v>
+        <v>8347.2990833835047</v>
       </c>
       <c r="U11">
-        <v>19057.322640766066</v>
+        <v>13797.501591914632</v>
       </c>
       <c r="V11">
-        <v>709.24036659990338</v>
+        <v>851.08843991988408</v>
       </c>
       <c r="W11">
-        <v>399.93244956595282</v>
+        <v>289.55109348574985</v>
       </c>
       <c r="X11">
-        <v>12.438454591087247</v>
+        <v>17.0655558681939</v>
       </c>
       <c r="Y11">
-        <v>12.094527123729897</v>
+        <v>4.9315446572301678</v>
       </c>
       <c r="Z11">
-        <v>1518.953463009377</v>
+        <v>1822.7441556112517</v>
       </c>
       <c r="AA11">
-        <v>4161.42073239026</v>
+        <v>3012.86861025055</v>
       </c>
       <c r="AB11">
-        <v>26.990752488492443</v>
+        <v>32.388902986190836</v>
       </c>
       <c r="AC11">
-        <v>15.342143278299687</v>
+        <v>11.107711733488936</v>
       </c>
       <c r="AD11">
-        <v>1.02607332450198</v>
+        <v>1.0272879989547392</v>
       </c>
       <c r="AE11">
-        <v>0.21184741613854261</v>
+        <v>0.21157804075144279</v>
       </c>
       <c r="AF11">
-        <v>11.955042856772828</v>
+        <v>16.484774919531283</v>
       </c>
       <c r="AG11">
-        <v>12.037800288867087</v>
+        <v>4.8905266522696085</v>
       </c>
       <c r="AH11">
-        <v>1519.4368747436915</v>
+        <v>1823.3249365599143</v>
       </c>
       <c r="AI11">
-        <v>4161.4774592251224</v>
+        <v>3012.9096282555111</v>
       </c>
       <c r="AJ11">
         <v>4.93950906538322E-15</v>
       </c>
       <c r="AK11">
-        <v>3.3831476626990771E-15</v>
+        <v>0</v>
       </c>
       <c r="AL11">
-        <v>1531.391917600464</v>
+        <v>1839.8097114794457</v>
       </c>
       <c r="AM11">
-        <v>4173.51525951399</v>
+        <v>3017.8001549077808</v>
       </c>
       <c r="AN11">
-        <v>95.0673420544445</v>
+        <v>114.21362300929796</v>
       </c>
       <c r="AO11">
-        <v>202.40970700618144</v>
+        <v>146.35912586293617</v>
       </c>
       <c r="AP11">
         <v>10.226838987634446</v>
@@ -4197,106 +4197,106 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>142</v>
       </c>
       <c r="C3">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3">
-        <v>28.118206703540103</v>
+        <v>28.321637242839358</v>
       </c>
       <c r="E3">
-        <v>27.277725087198327</v>
+        <v>27.259899548519414</v>
       </c>
       <c r="F3">
-        <v>70.739604742402236</v>
+        <v>70.6493051746511</v>
       </c>
       <c r="G3">
-        <v>70.628464807371074</v>
+        <v>70.586764589953845</v>
       </c>
       <c r="H3">
-        <v>37.560841960432178</v>
+        <v>48.292511091984224</v>
       </c>
       <c r="I3">
-        <v>109.32280890054773</v>
+        <v>69.814217961473943</v>
       </c>
       <c r="J3">
-        <v>62.597088467412078</v>
+        <v>80.487169601993415</v>
       </c>
       <c r="K3">
-        <v>53.412476074859008</v>
+        <v>34.980616976303814</v>
       </c>
       <c r="L3">
-        <v>459.47685198649066</v>
+        <v>590.75595255405938</v>
       </c>
       <c r="M3">
-        <v>3485.0998389755068</v>
+        <v>2463.9786960211127</v>
       </c>
       <c r="N3">
-        <v>12.232868807108174</v>
+        <v>12.232868807108176</v>
       </c>
       <c r="O3">
-        <v>31.878981833936816</v>
+        <v>35.29336527669517</v>
       </c>
       <c r="P3">
-        <v>1.6665517917131332</v>
+        <v>1.6666594422619077</v>
       </c>
       <c r="Q3">
-        <v>0.48857577491856247</v>
+        <v>0.50105290867266339</v>
       </c>
       <c r="R3">
-        <v>122.71624921467101</v>
+        <v>164.67148931400143</v>
       </c>
       <c r="S3">
-        <v>58.515565830312774</v>
+        <v>27.082850896314437</v>
       </c>
       <c r="T3">
-        <v>7191.2234535267562</v>
+        <v>9245.8587259629712</v>
       </c>
       <c r="U3">
-        <v>142139.48878733968</v>
+        <v>105910.79076673692</v>
       </c>
       <c r="V3">
-        <v>795.98880992712134</v>
+        <v>1023.4141841920133</v>
       </c>
       <c r="W3">
-        <v>1770.6773829845913</v>
+        <v>1234.5836925488545</v>
       </c>
       <c r="X3">
-        <v>18.394959273279884</v>
+        <v>30.526788115903535</v>
       </c>
       <c r="Y3">
-        <v>32.419523941719355</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="Z3">
-        <v>1570.5034032729534</v>
+        <v>2019.21866135094</v>
       </c>
       <c r="AA3">
-        <v>31038.054331183379</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AB3">
-        <v>30.246838998325174</v>
+        <v>38.825197795362634</v>
       </c>
       <c r="AC3">
-        <v>67.9420284885761</v>
+        <v>0</v>
       </c>
       <c r="AD3">
-        <v>1.1159912849093541</v>
+        <v>1.1180165935167421</v>
       </c>
       <c r="AE3">
-        <v>0.1255502938646294</v>
+        <v>0</v>
       </c>
       <c r="AF3">
-        <v>17.805745227229156</v>
+        <v>29.769093119297569</v>
       </c>
       <c r="AG3">
-        <v>32.270644646107591</v>
+        <v>9.5557110131730649</v>
       </c>
       <c r="AH3">
-        <v>1571.0926173190044</v>
+        <v>2019.9763563475462</v>
       </c>
       <c r="AI3">
-        <v>31038.203210478991</v>
+        <v>18948.690614068757</v>
       </c>
       <c r="AJ3">
         <v>0</v>
@@ -4305,16 +4305,16 @@
         <v>0</v>
       </c>
       <c r="AL3">
-        <v>1588.8983625462336</v>
+        <v>2049.7454494668432</v>
       </c>
       <c r="AM3">
-        <v>31070.4738551251</v>
+        <v>18958.246325081931</v>
       </c>
       <c r="AN3">
-        <v>106.30598317008956</v>
+        <v>137.13906149937242</v>
       </c>
       <c r="AO3">
-        <v>802.62996732164311</v>
+        <v>537.10763923259367</v>
       </c>
       <c r="AP3">
         <v>9.4801451504353054</v>
@@ -4334,124 +4334,124 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>98</v>
+        <v>172</v>
       </c>
       <c r="C4">
-        <v>41</v>
+        <v>57</v>
       </c>
       <c r="D4">
-        <v>28.018713250709638</v>
+        <v>28.229825711877151</v>
       </c>
       <c r="E4">
-        <v>27.102296834965461</v>
+        <v>27.071761041418288</v>
       </c>
       <c r="F4">
-        <v>63.79637077054727</v>
+        <v>63.732492283173976</v>
       </c>
       <c r="G4">
-        <v>63.656039358054585</v>
+        <v>63.638437772222545</v>
       </c>
       <c r="H4">
-        <v>36.927401065004595</v>
+        <v>47.478087083577321</v>
       </c>
       <c r="I4">
-        <v>88.8225275127105</v>
+        <v>59.215018341806989</v>
       </c>
       <c r="J4">
-        <v>67.458484450728932</v>
+        <v>86.73792793371706</v>
       </c>
       <c r="K4">
-        <v>54.756061318240157</v>
+        <v>36.504040878826764</v>
       </c>
       <c r="L4">
-        <v>447.90279610402382</v>
+        <v>575.87502356231641</v>
       </c>
       <c r="M4">
-        <v>2552.3118811767781</v>
+        <v>1701.5412541178519</v>
       </c>
       <c r="N4">
-        <v>12.129280241400279</v>
+        <v>12.129280241400281</v>
       </c>
       <c r="O4">
         <v>28.734961193392547</v>
       </c>
       <c r="P4">
-        <v>1.8267866815750018</v>
+        <v>1.8269044365883842</v>
       </c>
       <c r="Q4">
-        <v>0.61646592200840689</v>
+        <v>0.61646592200840677</v>
       </c>
       <c r="R4">
-        <v>143.13929937715912</v>
+        <v>190.69914932802081</v>
       </c>
       <c r="S4">
-        <v>56.806794491279014</v>
+        <v>30.579178240351204</v>
       </c>
       <c r="T4">
-        <v>6950.7174204389657</v>
+        <v>8936.6366834215278</v>
       </c>
       <c r="U4">
-        <v>93829.508196535928</v>
+        <v>62553.005464357258</v>
       </c>
       <c r="V4">
-        <v>850.46933396312443</v>
+        <v>1093.4605722383028</v>
       </c>
       <c r="W4">
-        <v>1636.1873341296166</v>
+        <v>1090.7915560864108</v>
       </c>
       <c r="X4">
-        <v>19.907038423333169</v>
+        <v>32.23724396542957</v>
       </c>
       <c r="Y4">
-        <v>23.051548665181226</v>
+        <v>8.0756810229526952</v>
       </c>
       <c r="Z4">
-        <v>1517.9788855864927</v>
+        <v>1951.687138611203</v>
       </c>
       <c r="AA4">
-        <v>20488.925337486471</v>
+        <v>13659.283558324305</v>
       </c>
       <c r="AB4">
-        <v>32.246471400090151</v>
+        <v>41.391936771866753</v>
       </c>
       <c r="AC4">
-        <v>62.774037046962746</v>
+        <v>41.849358031308576</v>
       </c>
       <c r="AD4">
-        <v>1.2325487418079597</v>
+        <v>1.2347883954903314</v>
       </c>
       <c r="AE4">
-        <v>0.17573851509306887</v>
+        <v>0.17564464381670725</v>
       </c>
       <c r="AF4">
-        <v>19.213244217584567</v>
+        <v>31.34506311307711</v>
       </c>
       <c r="AG4">
-        <v>22.859006548711257</v>
+        <v>7.9473881770507271</v>
       </c>
       <c r="AH4">
-        <v>1518.6726797922415</v>
+        <v>1952.5793194635558</v>
       </c>
       <c r="AI4">
-        <v>20489.117879602942</v>
+        <v>13659.411851170204</v>
       </c>
       <c r="AJ4">
-        <v>-7.0507433288103095E-15</v>
+        <v>0</v>
       </c>
       <c r="AK4">
-        <v>0</v>
+        <v>-6.9404441740299753E-15</v>
       </c>
       <c r="AL4">
-        <v>1537.8859240098261</v>
+        <v>1983.9243825766325</v>
       </c>
       <c r="AM4">
-        <v>20511.976886151653</v>
+        <v>13667.359239347255</v>
       </c>
       <c r="AN4">
-        <v>103.62870921633811</v>
+        <v>133.68437731548397</v>
       </c>
       <c r="AO4">
-        <v>587.8082179034426</v>
+        <v>391.66317915221271</v>
       </c>
       <c r="AP4">
         <v>9.39986679101518</v>
@@ -4471,43 +4471,43 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>100</v>
+        <v>266</v>
       </c>
       <c r="C5">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="D5">
-        <v>26.976058898859058</v>
+        <v>27.191154191894135</v>
       </c>
       <c r="E5">
-        <v>25.979886567667421</v>
+        <v>25.931469876663538</v>
       </c>
       <c r="F5">
-        <v>56.557931208200259</v>
+        <v>56.498569826328939</v>
       </c>
       <c r="G5">
-        <v>56.416737256794427</v>
+        <v>56.403947728372586</v>
       </c>
       <c r="H5">
-        <v>33.666766708926517</v>
+        <v>43.285842911476941</v>
       </c>
       <c r="I5">
-        <v>69.7722169687325</v>
+        <v>46.514811312488327</v>
       </c>
       <c r="J5">
-        <v>67.486716865014117</v>
+        <v>86.768635969303872</v>
       </c>
       <c r="K5">
-        <v>43.271836046223775</v>
+        <v>28.847890697482509</v>
       </c>
       <c r="L5">
-        <v>389.90856301663251</v>
+        <v>501.31100959281304</v>
       </c>
       <c r="M5">
-        <v>1776.9402929832165</v>
+        <v>1184.6268619888108</v>
       </c>
       <c r="N5">
-        <v>11.581408051081152</v>
+        <v>11.58140805108115</v>
       </c>
       <c r="O5">
         <v>25.467734439046545</v>
@@ -4519,58 +4519,58 @@
         <v>0.62018720238767078</v>
       </c>
       <c r="R5">
-        <v>154.8850352594369</v>
+        <v>204.67610842602153</v>
       </c>
       <c r="S5">
-        <v>41.655430021181168</v>
+        <v>23.273602248626645</v>
       </c>
       <c r="T5">
-        <v>5777.4336340439813</v>
+        <v>7428.1289580565453</v>
       </c>
       <c r="U5">
-        <v>57897.2892944596</v>
+        <v>38598.192862973061</v>
       </c>
       <c r="V5">
-        <v>812.218751320501</v>
+        <v>1044.2812516977867</v>
       </c>
       <c r="W5">
-        <v>1146.0000141920996</v>
+        <v>764.00000946139971</v>
       </c>
       <c r="X5">
-        <v>19.604537651955095</v>
+        <v>30.744040073544944</v>
       </c>
       <c r="Y5">
-        <v>14.818791081495675</v>
+        <v>5.3825096221696533</v>
       </c>
       <c r="Z5">
-        <v>1261.7434631376714</v>
+        <v>1622.2415954627224</v>
       </c>
       <c r="AA5">
-        <v>12642.64579872148</v>
+        <v>8428.4305324809848</v>
       </c>
       <c r="AB5">
-        <v>30.627545278992272</v>
+        <v>39.378272501561611</v>
       </c>
       <c r="AC5">
-        <v>43.964385076910709</v>
+        <v>29.309590051273762</v>
       </c>
       <c r="AD5">
-        <v>1.41160428996194</v>
+        <v>1.4165085019227341</v>
       </c>
       <c r="AE5">
-        <v>0.19947477922290915</v>
+        <v>0.19936829209814289</v>
       </c>
       <c r="AF5">
-        <v>18.849809741603625</v>
+        <v>29.770302994238737</v>
       </c>
       <c r="AG5">
-        <v>14.665728822568124</v>
+        <v>5.2805225902439483</v>
       </c>
       <c r="AH5">
-        <v>1262.4981910480231</v>
+        <v>1623.2153325420291</v>
       </c>
       <c r="AI5">
-        <v>12642.798860980411</v>
+        <v>8428.53251951291</v>
       </c>
       <c r="AJ5">
         <v>5.8605751304312572E-15</v>
@@ -4579,16 +4579,16 @@
         <v>0</v>
       </c>
       <c r="AL5">
-        <v>1281.3480007896264</v>
+        <v>1652.9856355362676</v>
       </c>
       <c r="AM5">
-        <v>12657.464589802978</v>
+        <v>8433.8130421031528</v>
       </c>
       <c r="AN5">
-        <v>90.207792954583979</v>
+        <v>116.37134164603774</v>
       </c>
       <c r="AO5">
-        <v>409.23767750384673</v>
+        <v>272.67973276673973</v>
       </c>
       <c r="AP5">
         <v>8.9752805414598669</v>
@@ -4608,43 +4608,43 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>100</v>
+        <v>272</v>
       </c>
       <c r="C6">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="D6">
-        <v>26.176934098656247</v>
+        <v>26.386993270422963</v>
       </c>
       <c r="E6">
-        <v>25.197208770838049</v>
+        <v>25.147980550060186</v>
       </c>
       <c r="F6">
-        <v>51.67246136267908</v>
+        <v>51.618081281948413</v>
       </c>
       <c r="G6">
-        <v>51.542563493307036</v>
+        <v>51.53102983393552</v>
       </c>
       <c r="H6">
-        <v>31.634784972071781</v>
+        <v>40.673294964092285</v>
       </c>
       <c r="I6">
-        <v>58.237071832669386</v>
+        <v>38.824714555112919</v>
       </c>
       <c r="J6">
-        <v>62.442851639252481</v>
+        <v>80.283666393324609</v>
       </c>
       <c r="K6">
-        <v>33.2282012062035</v>
+        <v>22.152134137468991</v>
       </c>
       <c r="L6">
-        <v>355.14686792490596</v>
+        <v>456.61740161773605</v>
       </c>
       <c r="M6">
-        <v>1355.0282421108079</v>
+        <v>903.35216140720513</v>
       </c>
       <c r="N6">
-        <v>11.226466948912126</v>
+        <v>11.226466948912124</v>
       </c>
       <c r="O6">
         <v>23.267451461230138</v>
@@ -4653,79 +4653,79 @@
         <v>1.9738667955030851</v>
       </c>
       <c r="Q6">
-        <v>0.57056785584407421</v>
+        <v>0.570567855844074</v>
       </c>
       <c r="R6">
-        <v>140.91615045249043</v>
+        <v>186.06776357160138</v>
       </c>
       <c r="S6">
-        <v>29.309074342817961</v>
+        <v>16.406627933932498</v>
       </c>
       <c r="T6">
-        <v>5101.0774776157059</v>
+        <v>6558.5281855059075</v>
       </c>
       <c r="U6">
-        <v>40335.945966013336</v>
+        <v>26890.630644008892</v>
       </c>
       <c r="V6">
-        <v>728.46814498257083</v>
+        <v>936.60190069187684</v>
       </c>
       <c r="W6">
-        <v>803.9787294267021</v>
+        <v>535.98581961780121</v>
       </c>
       <c r="X6">
-        <v>17.662278985244562</v>
+        <v>27.598500256571025</v>
       </c>
       <c r="Y6">
-        <v>10.350130827038949</v>
+        <v>3.7673322567464971</v>
       </c>
       <c r="Z6">
-        <v>1114.0329028470894</v>
+        <v>1432.3280179462595</v>
       </c>
       <c r="AA6">
-        <v>8807.8921141041137</v>
+        <v>5871.9280760694064</v>
       </c>
       <c r="AB6">
-        <v>27.45553485867956</v>
+        <v>35.299973389730923</v>
       </c>
       <c r="AC6">
-        <v>30.843170717373326</v>
+        <v>20.562113811582275</v>
       </c>
       <c r="AD6">
-        <v>1.4336145814080854</v>
+        <v>1.4385966152171854</v>
       </c>
       <c r="AE6">
-        <v>0.20086912366835222</v>
+        <v>0.20076189192008617</v>
       </c>
       <c r="AF6">
-        <v>16.975162558557741</v>
+        <v>26.711993486847092</v>
       </c>
       <c r="AG6">
-        <v>10.241999545672483</v>
+        <v>3.6952832192721137</v>
       </c>
       <c r="AH6">
-        <v>1114.7200192737764</v>
+        <v>1433.2145247159835</v>
       </c>
       <c r="AI6">
-        <v>8808.00024538548</v>
+        <v>5872.0001251068807</v>
       </c>
       <c r="AJ6">
-        <v>-5.1744857141339571E-15</v>
+        <v>0</v>
       </c>
       <c r="AK6">
         <v>0</v>
       </c>
       <c r="AL6">
-        <v>1131.6951818323341</v>
+        <v>1459.9265182028305</v>
       </c>
       <c r="AM6">
-        <v>8818.2422449311525</v>
+        <v>5875.6954083261544</v>
       </c>
       <c r="AN6">
-        <v>82.1649834353701</v>
+        <v>105.99571343122054</v>
       </c>
       <c r="AO6">
-        <v>312.06940018941623</v>
+        <v>207.93540150544661</v>
       </c>
       <c r="AP6">
         <v>8.70021070939704</v>
@@ -4745,40 +4745,40 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>98</v>
+        <v>328</v>
       </c>
       <c r="C7">
-        <v>51</v>
+        <v>93</v>
       </c>
       <c r="D7">
-        <v>26.148430245992834</v>
+        <v>26.361361914675783</v>
       </c>
       <c r="E7">
-        <v>25.139258064668752</v>
+        <v>25.0848411492262</v>
       </c>
       <c r="F7">
-        <v>48.107043535728224</v>
+        <v>48.0560469180964</v>
       </c>
       <c r="G7">
-        <v>47.983839480702187</v>
+        <v>47.973482611880748</v>
       </c>
       <c r="H7">
-        <v>31.406276844739608</v>
+        <v>40.379498800379494</v>
       </c>
       <c r="I7">
-        <v>50.473070239288788</v>
+        <v>33.648713492859187</v>
       </c>
       <c r="J7">
-        <v>64.044649555041445</v>
+        <v>82.343120856481818</v>
       </c>
       <c r="K7">
-        <v>27.314093374434588</v>
+        <v>18.209395582956393</v>
       </c>
       <c r="L7">
-        <v>351.30581675226841</v>
+        <v>451.67890725291647</v>
       </c>
       <c r="M7">
-        <v>1093.2982082906203</v>
+        <v>728.86547219374677</v>
       </c>
       <c r="N7">
         <v>11.185847290622426</v>
@@ -4787,64 +4787,64 @@
         <v>21.661020482950232</v>
       </c>
       <c r="P7">
-        <v>2.0392308795994256</v>
+        <v>2.0392308795994252</v>
       </c>
       <c r="Q7">
-        <v>0.541161717425563</v>
+        <v>0.54116171742556307</v>
       </c>
       <c r="R7">
-        <v>148.85113803545022</v>
+        <v>196.19950362636914</v>
       </c>
       <c r="S7">
-        <v>22.609622931678196</v>
+        <v>12.719947124013164</v>
       </c>
       <c r="T7">
-        <v>5027.6502185543923</v>
+        <v>6464.1217095699312</v>
       </c>
       <c r="U7">
-        <v>30297.907287509246</v>
+        <v>20198.604858339491</v>
       </c>
       <c r="V7">
-        <v>744.41579399698094</v>
+        <v>957.10602085326127</v>
       </c>
       <c r="W7">
-        <v>615.253939630881</v>
+        <v>410.16929308725389</v>
       </c>
       <c r="X7">
-        <v>18.249310989686141</v>
+        <v>28.282868853243983</v>
       </c>
       <c r="Y7">
-        <v>7.82828125124698</v>
+        <v>2.86571933705902</v>
       </c>
       <c r="Z7">
-        <v>1097.9970000561327</v>
+        <v>1411.7104286435988</v>
       </c>
       <c r="AA7">
-        <v>6615.9524037533256</v>
+        <v>4410.6349358355483</v>
       </c>
       <c r="AB7">
-        <v>28.022124292858173</v>
+        <v>36.028445519389379</v>
       </c>
       <c r="AC7">
-        <v>23.602803574038077</v>
+        <v>15.735202382691909</v>
       </c>
       <c r="AD7">
-        <v>1.485634049352915</v>
+        <v>1.4908002543296484</v>
       </c>
       <c r="AE7">
-        <v>0.20464476778976717</v>
+        <v>0.20453551970113268</v>
       </c>
       <c r="AF7">
-        <v>17.522556687718218</v>
+        <v>27.345219685131617</v>
       </c>
       <c r="AG7">
-        <v>7.7439781692803438</v>
+        <v>2.8095472857188177</v>
       </c>
       <c r="AH7">
-        <v>1098.7237543581007</v>
+        <v>1412.6480778117116</v>
       </c>
       <c r="AI7">
-        <v>6616.0367068352925</v>
+        <v>4410.6911078868889</v>
       </c>
       <c r="AJ7">
         <v>0</v>
@@ -4853,16 +4853,16 @@
         <v>0</v>
       </c>
       <c r="AL7">
-        <v>1116.2463110458189</v>
+        <v>1439.9932974968431</v>
       </c>
       <c r="AM7">
-        <v>6623.7806850045727</v>
+        <v>4413.5006551726074</v>
       </c>
       <c r="AN7">
-        <v>81.274990940706545</v>
+        <v>104.84732719885339</v>
       </c>
       <c r="AO7">
-        <v>251.79183835247949</v>
+        <v>167.77177512105632</v>
       </c>
       <c r="AP7">
         <v>8.6687315639390512</v>
@@ -4882,40 +4882,40 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>96</v>
+        <v>536</v>
       </c>
       <c r="C8">
-        <v>53</v>
+        <v>93</v>
       </c>
       <c r="D8">
-        <v>26.616235839390249</v>
+        <v>26.832055552301913</v>
       </c>
       <c r="E8">
-        <v>25.59810248305121</v>
+        <v>25.544280194064374</v>
       </c>
       <c r="F8">
-        <v>45.371288158693254</v>
+        <v>45.32371824620671</v>
       </c>
       <c r="G8">
-        <v>45.258330694202577</v>
+        <v>45.248018851449295</v>
       </c>
       <c r="H8">
-        <v>32.589049831481809</v>
+        <v>41.90020692619089</v>
       </c>
       <c r="I8">
-        <v>44.90175169639992</v>
+        <v>29.934501130933274</v>
       </c>
       <c r="J8">
-        <v>66.987498057083783</v>
+        <v>86.126783216250544</v>
       </c>
       <c r="K8">
-        <v>22.278478442797923</v>
+        <v>14.852318961865279</v>
       </c>
       <c r="L8">
-        <v>371.33698439059526</v>
+        <v>477.433265645051</v>
       </c>
       <c r="M8">
-        <v>917.36882469588</v>
+        <v>611.57921646391992</v>
       </c>
       <c r="N8">
         <v>11.394532406154251</v>
@@ -4924,82 +4924,82 @@
         <v>20.430579878010235</v>
       </c>
       <c r="P8">
-        <v>2.0555216676606585</v>
+        <v>2.055521667660658</v>
       </c>
       <c r="Q8">
         <v>0.49616056392259061</v>
       </c>
       <c r="R8">
-        <v>157.07433689288013</v>
+        <v>207.14202962568331</v>
       </c>
       <c r="S8">
-        <v>17.184897989589324</v>
+        <v>9.5942802633209254</v>
       </c>
       <c r="T8">
-        <v>5413.4676129507425</v>
+        <v>6960.1726452223811</v>
       </c>
       <c r="U8">
-        <v>23978.375307795068</v>
+        <v>15985.583538530043</v>
       </c>
       <c r="V8">
-        <v>793.159141776565</v>
+        <v>1019.7760394270119</v>
       </c>
       <c r="W8">
-        <v>473.32041543989521</v>
+        <v>315.54694362659671</v>
       </c>
       <c r="X8">
-        <v>19.380083174168181</v>
+        <v>30.106560558768031</v>
       </c>
       <c r="Y8">
-        <v>6.131195562073426</v>
+        <v>2.2251453116436632</v>
       </c>
       <c r="Z8">
-        <v>1182.2563107085093</v>
+        <v>1520.0438280537969</v>
       </c>
       <c r="AA8">
-        <v>5235.9982572495283</v>
+        <v>3490.6655048330176</v>
       </c>
       <c r="AB8">
-        <v>29.867924357928739</v>
+        <v>38.40161703162287</v>
       </c>
       <c r="AC8">
-        <v>18.158182053783229</v>
+        <v>12.105454702522133</v>
       </c>
       <c r="AD8">
-        <v>1.4703225448573825</v>
+        <v>1.4754345042512735</v>
       </c>
       <c r="AE8">
-        <v>0.19892866514192378</v>
+        <v>0.19882246965761119</v>
       </c>
       <c r="AF8">
-        <v>18.613445117226497</v>
+        <v>29.117454579505626</v>
       </c>
       <c r="AG8">
-        <v>6.0681508236565165</v>
+        <v>2.1831379232891024</v>
       </c>
       <c r="AH8">
-        <v>1183.0229487654513</v>
+        <v>1521.0329340330593</v>
       </c>
       <c r="AI8">
-        <v>5236.0613019879456</v>
+        <v>3490.7075122213723</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>-5.4913713720406992E-15</v>
       </c>
       <c r="AK8">
-        <v>3.54729718627758E-15</v>
+        <v>1.77364859313879E-15</v>
       </c>
       <c r="AL8">
-        <v>1201.6363938826776</v>
+        <v>1550.1503886125649</v>
       </c>
       <c r="AM8">
-        <v>5242.1294528116014</v>
+        <v>3492.8906501446613</v>
       </c>
       <c r="AN8">
-        <v>85.909681024916253</v>
+        <v>110.82630827787484</v>
       </c>
       <c r="AO8">
-        <v>211.27432780301692</v>
+        <v>140.77449457165812</v>
       </c>
       <c r="AP8">
         <v>8.830456930014055</v>
@@ -5019,40 +5019,40 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>90</v>
+        <v>428</v>
       </c>
       <c r="C9">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="D9">
-        <v>27.782988158907116</v>
+        <v>27.994630064061404</v>
       </c>
       <c r="E9">
-        <v>26.852370147830189</v>
+        <v>26.818484536200234</v>
       </c>
       <c r="F9">
-        <v>43.560521068315047</v>
+        <v>43.517388121595118</v>
       </c>
       <c r="G9">
-        <v>43.467671877156633</v>
+        <v>43.45515584513835</v>
       </c>
       <c r="H9">
-        <v>36.202163938314875</v>
+        <v>46.545639349261982</v>
       </c>
       <c r="I9">
-        <v>41.41613193467871</v>
+        <v>27.610754623119135</v>
       </c>
       <c r="J9">
-        <v>67.267255201485753</v>
+        <v>86.492042365156209</v>
       </c>
       <c r="K9">
-        <v>16.893502481894593</v>
+        <v>11.262334987929725</v>
       </c>
       <c r="L9">
-        <v>434.77288868388092</v>
+        <v>558.99371402213251</v>
       </c>
       <c r="M9">
-        <v>812.64965355238587</v>
+        <v>541.76643570159047</v>
       </c>
       <c r="N9">
         <v>12.009582891914787</v>
@@ -5061,82 +5061,82 @@
         <v>19.621572937668159</v>
       </c>
       <c r="P9">
-        <v>1.8581003974265979</v>
+        <v>1.8582200948224295</v>
       </c>
       <c r="Q9">
-        <v>0.40789667438134808</v>
+        <v>0.407896674381348</v>
       </c>
       <c r="R9">
-        <v>144.74008553325683</v>
+        <v>192.49816006513282</v>
       </c>
       <c r="S9">
-        <v>11.857849119468481</v>
+        <v>6.3198567218132364</v>
       </c>
       <c r="T9">
-        <v>6680.3806227841023</v>
+        <v>8589.0608007224182</v>
       </c>
       <c r="U9">
-        <v>20400.098130927832</v>
+        <v>13600.065420618552</v>
       </c>
       <c r="V9">
-        <v>839.6674194043494</v>
+        <v>1079.5723963770204</v>
       </c>
       <c r="W9">
-        <v>344.702146837974</v>
+        <v>229.80143122531592</v>
       </c>
       <c r="X9">
-        <v>19.750771909579818</v>
+        <v>31.776908899966688</v>
       </c>
       <c r="Y9">
-        <v>4.9670456384506272</v>
+        <v>1.725987734468003</v>
       </c>
       <c r="Z9">
-        <v>1458.9395769777943</v>
+        <v>1875.7794561143078</v>
       </c>
       <c r="AA9">
-        <v>4454.6336809789318</v>
+        <v>2969.7557873192873</v>
       </c>
       <c r="AB9">
-        <v>31.815742150520173</v>
+        <v>40.83904410167149</v>
       </c>
       <c r="AC9">
-        <v>13.225055716801199</v>
+        <v>8.8167038112007834</v>
       </c>
       <c r="AD9">
-        <v>1.2657973077624807</v>
+        <v>1.268098251500243</v>
       </c>
       <c r="AE9">
-        <v>0.17028937533427294</v>
+        <v>0.17019841723856033</v>
       </c>
       <c r="AF9">
-        <v>19.047773638292544</v>
+        <v>30.872891560995335</v>
       </c>
       <c r="AG9">
-        <v>4.9277391986541765</v>
+        <v>1.6997974380721614</v>
       </c>
       <c r="AH9">
-        <v>1459.6425752490816</v>
+        <v>1876.683473453279</v>
       </c>
       <c r="AI9">
-        <v>4454.6729874187295</v>
+        <v>2969.7819776156821</v>
       </c>
       <c r="AJ9">
         <v>0</v>
       </c>
       <c r="AK9">
-        <v>3.0179363601879143E-15</v>
+        <v>-1.5089681800939572E-15</v>
       </c>
       <c r="AL9">
-        <v>1478.6903488873741</v>
+        <v>1907.5563650142744</v>
       </c>
       <c r="AM9">
-        <v>4459.6007266173829</v>
+        <v>2971.481775053755</v>
       </c>
       <c r="AN9">
-        <v>100.59083741462813</v>
+        <v>129.76516335388061</v>
       </c>
       <c r="AO9">
-        <v>187.15655681538459</v>
+        <v>124.70450422599951</v>
       </c>
       <c r="AP9">
         <v>9.3071045563229013</v>
@@ -5156,124 +5156,124 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>82</v>
+        <v>362</v>
       </c>
       <c r="C10">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D10">
-        <v>30.129241090593958</v>
+        <v>30.34718590431212</v>
       </c>
       <c r="E10">
-        <v>29.22897523195336</v>
+        <v>29.209927394710725</v>
       </c>
       <c r="F10">
-        <v>42.792733933219765</v>
+        <v>42.752270416010248</v>
       </c>
       <c r="G10">
-        <v>42.713233872541956</v>
+        <v>42.698978000871726</v>
       </c>
       <c r="H10">
-        <v>43.127311408876366</v>
+        <v>55.449400382841034</v>
       </c>
       <c r="I10">
-        <v>39.98765244367096</v>
+        <v>26.658434962447302</v>
       </c>
       <c r="J10">
-        <v>76.984865991656633</v>
+        <v>98.986935663877588</v>
       </c>
       <c r="K10">
-        <v>13.969156160593098</v>
+        <v>9.3127707737287277</v>
       </c>
       <c r="L10">
-        <v>565.31334252189413</v>
+        <v>726.83144038529224</v>
       </c>
       <c r="M10">
-        <v>770.97077287503043</v>
+        <v>513.98051525002006</v>
       </c>
       <c r="N10">
         <v>13.108012627134054</v>
       </c>
       <c r="O10">
-        <v>19.280220912219509</v>
+        <v>19.280220912219505</v>
       </c>
       <c r="P10">
-        <v>1.7850606373717</v>
+        <v>1.7851759438413937</v>
       </c>
       <c r="Q10">
-        <v>0.34933674039182222</v>
+        <v>0.34933674039182211</v>
       </c>
       <c r="R10">
-        <v>161.6633016800335</v>
+        <v>216.94087365203333</v>
       </c>
       <c r="S10">
-        <v>9.3561021703729814</v>
+        <v>4.7596054726749548</v>
       </c>
       <c r="T10">
-        <v>9480.6238427123</v>
+        <v>12189.373512058673</v>
       </c>
       <c r="U10">
-        <v>19017.131216389058</v>
+        <v>12678.087477592704</v>
       </c>
       <c r="V10">
-        <v>1048.97914849381</v>
+        <v>1348.6874766348985</v>
       </c>
       <c r="W10">
-        <v>280.0745223587806</v>
+        <v>186.71634823918706</v>
       </c>
       <c r="X10">
-        <v>24.240647724991987</v>
+        <v>40.231777350303375</v>
       </c>
       <c r="Y10">
-        <v>4.4761626912070458</v>
+        <v>1.5063124865643345</v>
       </c>
       <c r="Z10">
-        <v>2070.4894106479551</v>
+        <v>2662.0578136902295</v>
       </c>
       <c r="AA10">
-        <v>4152.6443984938614</v>
+        <v>2768.4295989959096</v>
       </c>
       <c r="AB10">
-        <v>39.860552976951638</v>
+        <v>51.1654740314848</v>
       </c>
       <c r="AC10">
-        <v>10.746105625253557</v>
+        <v>7.1640704168358029</v>
       </c>
       <c r="AD10">
-        <v>1.1155471588685226</v>
+        <v>1.1175716522209696</v>
       </c>
       <c r="AE10">
-        <v>0.14842719828313675</v>
+        <v>0.14834792568639738</v>
       </c>
       <c r="AF10">
-        <v>23.464465838368149</v>
+        <v>39.233652591619595</v>
       </c>
       <c r="AG10">
-        <v>4.4483243769022689</v>
+        <v>1.4877635224049202</v>
       </c>
       <c r="AH10">
-        <v>2071.2655925345794</v>
+        <v>2663.0559384489129</v>
       </c>
       <c r="AI10">
-        <v>4152.6722368081655</v>
+        <v>2768.4481479600695</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>-9.6170569552145811E-15</v>
       </c>
       <c r="AK10">
-        <v>-1.4066719531460129E-15</v>
+        <v>0</v>
       </c>
       <c r="AL10">
-        <v>2094.7300583729475</v>
+        <v>2702.2895910405327</v>
       </c>
       <c r="AM10">
-        <v>4157.1205611850673</v>
+        <v>2769.9359114824738</v>
       </c>
       <c r="AN10">
-        <v>130.79263511265259</v>
+        <v>168.7278470135584</v>
       </c>
       <c r="AO10">
-        <v>177.55740721643829</v>
+        <v>118.3084857318466</v>
       </c>
       <c r="AP10">
         <v>10.158358133192948</v>
@@ -5293,124 +5293,124 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>74</v>
+        <v>242</v>
       </c>
       <c r="C11">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="D11">
-        <v>32.86015729733306</v>
+        <v>33.091531691709164</v>
       </c>
       <c r="E11">
-        <v>31.935539236820564</v>
+        <v>31.923913135212658</v>
       </c>
       <c r="F11">
-        <v>42.345952682985889</v>
+        <v>42.306195578866941</v>
       </c>
       <c r="G11">
-        <v>42.269023146977709</v>
+        <v>42.254625046756743</v>
       </c>
       <c r="H11">
-        <v>51.59400759038985</v>
+        <v>66.335152616215524</v>
       </c>
       <c r="I11">
-        <v>39.1596734538681</v>
+        <v>26.1064489692454</v>
       </c>
       <c r="J11">
-        <v>94.295484637780419</v>
+        <v>121.24489209572087</v>
       </c>
       <c r="K11">
-        <v>13.238234398931882</v>
+        <v>8.8254895992879181</v>
       </c>
       <c r="L11">
-        <v>739.7067019475827</v>
+        <v>951.05147393260586</v>
       </c>
       <c r="M11">
-        <v>747.14972994004972</v>
+        <v>498.09981996003307</v>
       </c>
       <c r="N11">
-        <v>14.337066192263846</v>
+        <v>14.337066192263842</v>
       </c>
       <c r="O11">
         <v>19.079569977012866</v>
       </c>
       <c r="P11">
-        <v>1.8276441207359193</v>
+        <v>1.82776231475923</v>
       </c>
       <c r="Q11">
         <v>0.33805783428013331</v>
       </c>
       <c r="R11">
-        <v>204.70178042679308</v>
+        <v>276.19463409721163</v>
       </c>
       <c r="S11">
-        <v>8.7475650590892453</v>
+        <v>4.4144923618454186</v>
       </c>
       <c r="T11">
-        <v>13568.463561218276</v>
+        <v>17445.167435852069</v>
       </c>
       <c r="U11">
-        <v>18237.752129103974</v>
+        <v>12158.501419402648</v>
       </c>
       <c r="V11">
-        <v>1405.3895819969282</v>
+        <v>1806.9294625674791</v>
       </c>
       <c r="W11">
-        <v>262.65774228293679</v>
+        <v>175.10516152195788</v>
       </c>
       <c r="X11">
-        <v>32.363192316609535</v>
+        <v>54.587789467603862</v>
       </c>
       <c r="Y11">
-        <v>4.2722762084935706</v>
+        <v>1.4309664614483033</v>
       </c>
       <c r="Z11">
-        <v>2963.239612534599</v>
+        <v>3809.8795018302076</v>
       </c>
       <c r="AA11">
-        <v>3982.4565734065291</v>
+        <v>2654.9710489376848</v>
       </c>
       <c r="AB11">
-        <v>53.468977113471865</v>
+        <v>68.633419117242056</v>
       </c>
       <c r="AC11">
-        <v>10.077922696417149</v>
+        <v>6.7186151309447872</v>
       </c>
       <c r="AD11">
-        <v>1.0448029503606693</v>
+        <v>1.0466977190041245</v>
       </c>
       <c r="AE11">
-        <v>0.14514598943110932</v>
+        <v>0.14506847036667978</v>
       </c>
       <c r="AF11">
-        <v>31.388063983466676</v>
+        <v>53.333832605502089</v>
       </c>
       <c r="AG11">
-        <v>4.2467460001130908</v>
+        <v>1.4139554126233485</v>
       </c>
       <c r="AH11">
-        <v>2964.214740867742</v>
+        <v>3811.13345869231</v>
       </c>
       <c r="AI11">
-        <v>3982.4821036149096</v>
+        <v>2654.9880599865096</v>
       </c>
       <c r="AJ11">
-        <v>6.8818618388333014E-15</v>
+        <v>0</v>
       </c>
       <c r="AK11">
         <v>0</v>
       </c>
       <c r="AL11">
-        <v>2995.6028048512085</v>
+        <v>3864.4672912978117</v>
       </c>
       <c r="AM11">
-        <v>3986.7288496150227</v>
+        <v>2656.4020153991337</v>
       </c>
       <c r="AN11">
-        <v>171.13942984621221</v>
+        <v>220.7776883883835</v>
       </c>
       <c r="AO11">
-        <v>172.07128874621429</v>
+        <v>114.65302393512634</v>
       </c>
       <c r="AP11">
         <v>11.110841673956502</v>
